--- a/salida/Productos_a_registrar_Guillermo.xlsx
+++ b/salida/Productos_a_registrar_Guillermo.xlsx
@@ -143,9 +143,9 @@
     <t>Septiembre 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Cortisol Support
-Cóctel de Calma
-Armonía Cortisol</t>
+    <t xml:space="preserve">Pispa Chill
+Nuara Armonía
+Garra Calm</t>
   </si>
   <si>
     <t>C6</t>
@@ -177,9 +177,9 @@
 • Beyond Vitamins Aguaje + Fenogreco 1000 mg (México): 1.313 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Aguaje Curvas
-Aguaje Amazónico
-Silueta Plena</t>
+    <t xml:space="preserve">Pispa Booty
+Nuara Silueta
+Garra Aguaje</t>
   </si>
   <si>
     <t>F65</t>
@@ -217,9 +217,9 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Feliz y Limpio
-Happy Cleaner
-Vientre Feliz</t>
+    <t xml:space="preserve">Pispa Detox
+Nuara Dicha
+Garra Limpio</t>
   </si>
   <si>
     <t>C2</t>
@@ -252,7 +252,9 @@
     <t>Últimos 28 días</t>
   </si>
   <si>
-    <t>Magnesio Kids</t>
+    <t xml:space="preserve">Pispa Kids Calm
+Nuara Cuento
+Garra Osito</t>
   </si>
   <si>
     <t>N6</t>
@@ -292,9 +294,9 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Gladiador
-Furia Espartana
-Elixir del Guerrero</t>
+    <t xml:space="preserve">Pispa Papi Shot
+Nuara Gladiador
+Garra Toro</t>
   </si>
   <si>
     <t>C4</t>
@@ -324,9 +326,9 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Genio Kids
-Mente Brillante Kids
-Estrellitas de Atención</t>
+    <t xml:space="preserve">Pispa Kids Focus
+Nuara Foco
+Garra Junior</t>
   </si>
   <si>
     <t>C5</t>
@@ -351,9 +353,9 @@
     <t>• Bcuelov Cayenne Pepper Supplement (EE. UU.):  u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cayena Térmica
-Fuego Natural
-Metabolismo Activo</t>
+    <t xml:space="preserve">Pispa Picante
+Nuara Cayena
+Garra Fuego</t>
   </si>
   <si>
     <t>F39</t>
@@ -387,9 +389,9 @@
 • k2o Advanced Skin Hydration Mix (EE. UU.): 6.716 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Colágeno Firmeza Total
-Seda Marina
-Rodillas Sanas</t>
+    <t xml:space="preserve">Pispa Glow Shake
+Nuara Piel
+Garra Flex</t>
   </si>
   <si>
     <t>F06</t>
@@ -424,9 +426,9 @@
 • NUTRAHARMONY Biotin Gummies Sugar (EE. UU.): 515 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cabello Fuerte
-Biotina Brillante
-Melena Sana</t>
+    <t xml:space="preserve">Pispa Melena
+Nuara Cabellera
+Garra Tupido</t>
   </si>
   <si>
     <t>N4</t>
@@ -455,9 +457,9 @@
 • Lemme Sleep Gummies with 5mg Melatonin, Magnesium, L (EE. UU.): 1.300 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Noche Plena
-Sueño Dulce
-Melatonina Serena</t>
+    <t xml:space="preserve">Pispa Sleep
+Nuara Sueño
+Garra Noche</t>
   </si>
   <si>
     <t>N1</t>
@@ -484,9 +486,9 @@
 • First Day Kids Calming Magnesium Gummies Ages 4 (EE. UU.): 288 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Gotitas de Calma
-Magnesio Infantil
-Pequeño Sereno</t>
+    <t xml:space="preserve">Pispa Kids Calm Gotas
+Nuara Nana
+Garra Mini</t>
   </si>
   <si>
     <t>N5</t>
@@ -520,9 +522,9 @@
 • Gardenika Organic Laxative Loose Leaf Tea, Caffeine (EE. UU.): 15 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Té Vientre Libre
-Hoja de Sen
-Té Despeje</t>
+    <t xml:space="preserve">Pispa Fluye Té
+Nuara Alivio
+Garra Libre</t>
   </si>
   <si>
     <t>N3</t>
@@ -550,9 +552,9 @@
 • $1 AUCTIONS Soursop Sleep Drops with Melatonin 5mg, Ashwagandha &amp; L (EE. UU.): 13 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Gotas de Sueño
-Luna Líquida
-Descanso Rápido</t>
+    <t xml:space="preserve">Pispa Sleep Gotas
+Nuara Luna
+Garra Off</t>
   </si>
   <si>
     <t>N2</t>
@@ -576,9 +578,9 @@
 • UPMER Pack Magnesio 7 en 1 + Omega 3 (México): 3.051 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Magnesio Reparador
-Reposo Profundo
-Piernas en Calma</t>
+    <t xml:space="preserve">Pispa Magnesio
+Nuara Reposo
+Garra Mag</t>
   </si>
   <si>
     <t>F01</t>
@@ -608,9 +610,9 @@
 • Vital Source Feminine Balance Gummies (EE. UU.): 10.985 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Equilibrio Íntimo
-Pétalo Íntimo
-Frescura Femenina</t>
+    <t xml:space="preserve">Pispa Miau
+Nuara Íntima
+Garra Flora</t>
   </si>
   <si>
     <t>F02</t>
@@ -630,9 +632,9 @@
 • LeeFar Cutting Drops Lymphatic Debloat (EE. UU.): 15.488 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Gotas Drenantes
-Manantial Depurativo
-Piernas Livianas</t>
+    <t xml:space="preserve">Pispa Drena Gotas
+Nuara Fluida
+Garra Desinfla Gotas</t>
   </si>
   <si>
     <t>F09</t>
@@ -659,9 +661,9 @@
 • NeoCell Creatine Monohydrate + Multi Collagen (EE. UU.): 11.436 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Glúteo Activo
-Silueta Esculpida
-Curvas de Mujer</t>
+    <t xml:space="preserve">Pispa Power
+Nuara Curva
+Garra Glute</t>
   </si>
   <si>
     <t>F04</t>
@@ -685,9 +687,9 @@
 • Windboss Hack your Tummy (paquete) (México): 14.245 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Digestión Ligera
-Jardín Intestinal
-Vientre Sereno</t>
+    <t xml:space="preserve">Pispa Pancita
+Nuara Ligera
+Garra Gut</t>
   </si>
   <si>
     <t>F03</t>
@@ -708,9 +710,9 @@
 • HS Hero Sport Creatina Monohidratada 650 g (México): 1.209 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Creatina Fuerza Real
-Roble Atlético
-Músculo Firme</t>
+    <t xml:space="preserve">Pispa Power Pura
+Nuara Fuerza
+Garra Crea</t>
   </si>
   <si>
     <t>F05</t>
@@ -730,9 +732,9 @@
 • Toplux Organic Beet Root Capsules (EE. UU.): 18.180 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Potencia Circulatoria
-Raíz Roja Vital
-Hombre Vigoroso</t>
+    <t xml:space="preserve">Pispa Firme
+Nuara Vigor
+Garra Pump</t>
   </si>
   <si>
     <t>F11</t>
@@ -768,9 +770,9 @@
 • Toyocare Bebida relajante Ashwagandha KSM-66 (México): 1.565 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Bebida Relajante Nocturna
-Tisana de Luna
-Noche Tranquila</t>
+    <t xml:space="preserve">Pispa Relax
+Nuara Ocaso
+Garra Chill</t>
   </si>
   <si>
     <t>F07</t>
@@ -796,9 +798,9 @@
 • SWIYIE Complejo de Colágeno Múltiple (120 cápsulas) (México): 6.545 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Colágeno Belleza Integral
-Esencia de Perla
-Mujer Radiante</t>
+    <t xml:space="preserve">Pispa Glow
+Nuara Lozana
+Garra Piel</t>
   </si>
   <si>
     <t>F08</t>
@@ -816,9 +818,9 @@
     <t>• Vitafusion Fiber Well Sugar Free Gummies (EE. UU.): 38.736 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Gomitas de Fibra Diaria
-Fibra Suave
-Tránsito Ligero</t>
+    <t xml:space="preserve">Pispa Fluye
+Nuara Ritmo
+Garra Fibra</t>
   </si>
   <si>
     <t>F40</t>
@@ -844,9 +846,9 @@
 • VEV DeepCalm Magnesium Complex Gummies 14-in-1 (EE. UU.): 18.378 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Gomas Sueño Profundo
-Sueño de Algodón
-Dulces Sueños</t>
+    <t xml:space="preserve">Pispa Mimir
+Nuara Arrullo
+Garra Rest</t>
   </si>
   <si>
     <t>F16</t>
@@ -867,9 +869,9 @@
     <t>• Toplux Organic Beet Root Tablets 2040mg (EE. UU.): 22.673 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Remolacha Roja Pura
-Raíz Carmesí
-Presión Serena</t>
+    <t xml:space="preserve">Pispa Red Tabs
+Nuara Pulso
+Garra Bombeo</t>
   </si>
   <si>
     <t>F35</t>
@@ -891,9 +893,9 @@
     <t>• Windboss Combo Cortisol + Myo-Inositol (kit 2 frascos) (México): 28.383 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Control de Cortisol
-Armonía Hormonal
-Vientre sin Estrés</t>
+    <t xml:space="preserve">Pispa Cortisol
+Nuara Calma
+Garra Temple</t>
   </si>
   <si>
     <t>F14</t>
@@ -911,9 +913,9 @@
     <t>• Body Magic Chlorophyll Pill (EE. UU.): 19.913 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Clorofila Sin Olor
-Frescura Verde
-Cuerpo Fresco</t>
+    <t xml:space="preserve">Pispa Fresh
+Nuara Fresca
+Garra Verde</t>
   </si>
   <si>
     <t>F72</t>
@@ -944,9 +946,9 @@
 • Windboss Cápsulas de Vitalidad y Resistencia 2026 (México): 1.588 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Vigor Masculino
-Potencia Andina
-Hombre de Hierro</t>
+    <t xml:space="preserve">Pispa Papi
+Nuara Potencia
+Garra Rey</t>
   </si>
   <si>
     <t>F24</t>
@@ -1025,9 +1027,9 @@
     <t>• YESNAP Lymphatic Drainage Support 12-in-1 (30 sticks, naranja-mango) (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Drenaje Linfático Express
-Doce Plantas
-Cuerpo Ligero</t>
+    <t xml:space="preserve">Pispa Drena Stick
+Nuara Cauce
+Garra Seco</t>
   </si>
   <si>
     <t>F27</t>
@@ -1047,9 +1049,9 @@
 • Micro Ingredients Oregano Oil with Black Seed Oil (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Orégano y Semilla Negra
-Semilla Negra Ancestral
-Escudo Natural</t>
+    <t xml:space="preserve">Pispa Orégano
+Nuara Guardiana
+Garra Escudo</t>
   </si>
   <si>
     <t>F76</t>
@@ -1067,9 +1069,9 @@
     <t>• Bella All Natural Colon Cleanse 400g (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Colon Limpio Papaya
-Hoja de Papaya
-Vientre en Paz</t>
+    <t xml:space="preserve">Pispa Papaya
+Nuara Limpia
+Garra Reset</t>
   </si>
   <si>
     <t>F80</t>
@@ -1087,9 +1089,9 @@
     <t>• Nutricost NAC N-Acetyl L-Cysteine Capsules (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">NAC Depura
-Hígado Puro
-Respiro Limpio</t>
+    <t xml:space="preserve">Pispa Respira
+Nuara Respiro
+Garra Filtro</t>
   </si>
   <si>
     <t>F77</t>
@@ -1110,9 +1112,9 @@
     <t>• Milamiamor 15 Day Cleanse (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Limpieza 15 Días
-Depuración Herbal
-Ligereza Total</t>
+    <t xml:space="preserve">Pispa Reset
+Nuara Reinicio
+Garra Purga</t>
   </si>
   <si>
     <t>F50</t>
@@ -1139,9 +1141,9 @@
     <t>• ATRAKT D-BLOAT Advanced Debloat Powder (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Vientre Desinflamado
-Botánica Depurativa
-Adiós Hinchazón</t>
+    <t xml:space="preserve">Pispa Planita
+Nuara Vientre
+Garra Flat</t>
   </si>
   <si>
     <t>F31</t>
@@ -1160,9 +1162,9 @@
     <t>• BioGaia Fresh Breath Oral Probiotics (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Aliento Fresco Diario
-Boca Equilibrada
-Sonrisa Segura</t>
+    <t xml:space="preserve">Pispa Besito
+Nuara Aliento
+Garra Fresh</t>
   </si>
   <si>
     <t>F73</t>
@@ -1180,9 +1182,9 @@
     <t>• Horbäach Liquid Chlorophyll Drops (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Gotas de Clorofila
-Hoja Viva
-Agua Verde</t>
+    <t xml:space="preserve">Pispa Fresh Gotas
+Nuara Rocío
+Garra Verde Gotas</t>
   </si>
   <si>
     <t>F33</t>
@@ -1198,9 +1200,9 @@
 • MVPCARE Desintoxicación Linfática (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Drenaje Linfático Total
-Jardín Depurativo
-Menos Retención</t>
+    <t xml:space="preserve">Pispa Drena
+Nuara Liviana
+Garra Desinfla</t>
   </si>
   <si>
     <t xml:space="preserve">• LeafLea Senna Tea Bags (EE. UU.)
@@ -1261,9 +1263,9 @@
     <t>• Loosey Goosey Calming Pouches 3 Pack (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Bolsitas Calma
-Kava Serena
-Pausa Serena</t>
+    <t xml:space="preserve">Pispa Calma
+Nuara Pausa
+Garra Frío</t>
   </si>
   <si>
     <t>F43</t>
@@ -1288,9 +1290,9 @@
     <t>• Windboss Ashwagandha KSM-66 + L-Teanina + PS (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cortisol en Calma
-Raíz de Calma
-Mente Tranquila</t>
+    <t xml:space="preserve">Pispa Zen
+Nuara Sosiego
+Garra Aplomo</t>
   </si>
   <si>
     <t xml:space="preserve">• Project Superhuman DreamOn Sleep Gummies for Adult Men &amp; Women, 8 (EE. UU.)
@@ -1346,9 +1348,9 @@
 • Wellah Electrolytes Sample Pack + Shaker (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Hidratación Inmediata
-Brisa Mineral
-Suero Recuperador</t>
+    <t xml:space="preserve">Pispa Suero
+Nuara Oasis
+Garra Hidra</t>
   </si>
   <si>
     <t>F68</t>
@@ -1371,9 +1373,9 @@
 • Windboss NAD+ Liposomal NR 900 mg (100 cápsulas) (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">NAD+ Celular
-Longevidad Activa
-Energía de Juventud</t>
+    <t xml:space="preserve">Pispa Young
+Nuara Longeva
+Garra Cell</t>
   </si>
   <si>
     <t>F20</t>
@@ -1399,9 +1401,9 @@
 • Montue Gotitas B12 + B6 (40 porciones, frambuesa) (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Complejo B Energía
-Claridad Andina
-Energía Constante</t>
+    <t xml:space="preserve">Pispa Pila
+Nuara Despierta
+Garra Boost</t>
   </si>
   <si>
     <t>F28</t>
@@ -1417,9 +1419,9 @@
 • Vital Source Creatine Gummies (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Creatina Masticable
-Fuerza Pura
-Rendimiento Diario</t>
+    <t xml:space="preserve">Pispa Power Gummies
+Nuara Tono
+Garra Crea Gum</t>
   </si>
   <si>
     <t>F22</t>
@@ -1437,9 +1439,9 @@
     <t>• BODYHEALTH Perfect Amino Tablets (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Músculo Esencial
-Ocho Esenciales
-Recuperación Activa</t>
+    <t xml:space="preserve">Pispa Amino
+Nuara Esencial
+Garra Recarga</t>
   </si>
   <si>
     <t>F23</t>
@@ -1461,9 +1463,9 @@
 • Euphoric 100% Whey Protein + Creatina (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Proteína con Colágeno
-Suero Dorado
-Batido Atleta</t>
+    <t xml:space="preserve">Pispa Protein
+Nuara Esculpida
+Garra Whey</t>
   </si>
   <si>
     <t>F69</t>
@@ -1478,9 +1480,9 @@
     <t>• Cata-Kor NMN Powder 1000 mg (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">NMN Polvo Puro
-Origen Celular
-Juventud Diaria</t>
+    <t xml:space="preserve">Pispa Young Drink
+Nuara Aurora
+Garra Motor</t>
   </si>
   <si>
     <t>F59</t>
@@ -1500,9 +1502,9 @@
     <t>• Toyocare palitos de miel con shilajit (30 unidades) (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Miel con Shilajit
-Néctar Negro
-Miel Potente</t>
+    <t xml:space="preserve">Pispa Honey
+Nuara Brío
+Garra Roca</t>
   </si>
   <si>
     <t>Salud íntima y libido femenina  ·  6 registros</t>
@@ -1535,9 +1537,9 @@
 • VivoNu Probióticos para la Mujer con Arándano (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Equilibrio Femenino
-Arándano Íntimo
-Mujer Protegida</t>
+    <t xml:space="preserve">Pispa Arándano
+Nuara Flora
+Garra Berry</t>
   </si>
   <si>
     <t>F63</t>
@@ -1562,9 +1564,9 @@
     <t>• Adapto Drive Maca Root Drops (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Gotas del Deseo
-Raíz del Deseo
-Pasión Diaria</t>
+    <t xml:space="preserve">Pispa Fuego
+Nuara Deseo
+Garra Ganas</t>
   </si>
   <si>
     <t>F45</t>
@@ -1587,9 +1589,9 @@
     <t>• Nello Superbalance Hormonal Support Drink Mix (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Súper Balance Hormonal
-Luna Botánica
-Equilibrio Mensual</t>
+    <t xml:space="preserve">Pispa Balance
+Nuara Equilibrio
+Garra Ella</t>
   </si>
   <si>
     <t>F44</t>
@@ -1609,9 +1611,9 @@
 • Zesty Pro Inositol 200 g + Pink Fury 100 g (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ciclo Regular
-Armonía Ovárica
-Fertilidad Plena</t>
+    <t xml:space="preserve">Pispa Hormonita
+Nuara Ciclo
+Garra Ritmo</t>
   </si>
   <si>
     <t>F64</t>
@@ -1631,9 +1633,9 @@
     <t>• Montue Maca &amp; Fenogreco Gummies Combo (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Gomitas Curvas Plenas
-Maca Florecer
-Curvas y Deseo</t>
+    <t xml:space="preserve">Pispa Curvas
+Nuara Diosa
+Garra Curva</t>
   </si>
   <si>
     <t>Quemar grasa y bajar de peso  ·  8 registros</t>
@@ -1660,9 +1662,9 @@
     <t>• Apothékary Blue Burn Metabolic Support Drops (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Gotas Sin Antojos
-Fuego Azul
-Metabolismo en Marcha</t>
+    <t xml:space="preserve">Pispa Slim Gotas
+Nuara Templanza
+Garra Cut</t>
   </si>
   <si>
     <t>F79</t>
@@ -1683,9 +1685,9 @@
     <t>• Coleology Cutting Jelly (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Jalea Saciante
-Jalea Silueta
-Cintura Fina</t>
+    <t xml:space="preserve">Pispa Jelly
+Nuara Saciada
+Garra Full</t>
   </si>
   <si>
     <t>F34</t>
@@ -1704,9 +1706,9 @@
     <t>• Yesnap MOCKTALE-1 Metabolic Drink Mix (30 sobres) (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Control de Antojos
-Berberina Esbelta
-Saciedad Natural</t>
+    <t xml:space="preserve">Pispa Slim
+Nuara Mesura
+Garra Lean</t>
   </si>
   <si>
     <t>F42</t>
@@ -1729,9 +1731,9 @@
     <t>• Blood Sugar Complex 20 Vitamins &amp; Minerals (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Glucosa Estable
-Canela y Gymnema
-Azúcar en Balance</t>
+    <t xml:space="preserve">Pispa Glucosa
+Nuara Balance
+Garra Nivel</t>
   </si>
   <si>
     <t>F13</t>
@@ -1754,9 +1756,9 @@
 • Multiblue Berberina HCl con Canela y Cúrcuma (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Berberina Equilibrio Azúcar
-Raíz Dorada
-Azúcar en Orden</t>
+    <t xml:space="preserve">Pispa Berberina
+Nuara Esbelta
+Garra Freno</t>
   </si>
   <si>
     <t>F10</t>
@@ -1785,9 +1787,9 @@
     <t>• Leefar Cutting Bundle (Cutting Mix + Cutting Drops) (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Berberina Termogénica
-Silueta Botánica
-Una Talla Menos</t>
+    <t xml:space="preserve">Pispa Burn Drink
+Nuara Contorno
+Garra Shred</t>
   </si>
   <si>
     <t>F41</t>
@@ -1808,9 +1810,9 @@
     <t>• Toplux Keto Burn (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Quemador Keto Total
-Mango y Frambuesa
-Cintura Definida</t>
+    <t xml:space="preserve">Pispa Burn
+Nuara Brasa
+Garra Quema</t>
   </si>
   <si>
     <t>F12</t>
@@ -1832,9 +1834,9 @@
     <t>• Montue Gomitas de ACV (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Vinagre Adelgazante
-Manzana Dorada
-Sin Antojos</t>
+    <t xml:space="preserve">Pispa Manzanita
+Nuara Manzana
+Garra Apple</t>
   </si>
   <si>
     <t>Colágeno y antiedad  ·  7 registros</t>
@@ -1861,9 +1863,9 @@
     <t>• Cymbiotika Liposomal Glutathione (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Glutatión Luminoso
-Piel de Porcelana
-Tono Uniforme</t>
+    <t xml:space="preserve">Pispa Bright Shot
+Nuara Luz
+Garra Glow</t>
   </si>
   <si>
     <t>F25</t>
@@ -1886,9 +1888,9 @@
 • Cata-Kor Liposomal Glutathione 1155 mg (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Glutatión Radiante
-Piel Luminosa
-Tono Parejo</t>
+    <t xml:space="preserve">Pispa Bright
+Nuara Luminosa
+Garra Parejo</t>
   </si>
   <si>
     <t>F51</t>
@@ -1903,9 +1905,9 @@
     <t>• Youtheory Collagen Liquid 5,000 mg (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Colágeno Líquido Total
-Piel de Nácar
-Firmeza Diaria</t>
+    <t xml:space="preserve">Pispa Glow Shot
+Nuara Firme
+Garra Joint</t>
   </si>
   <si>
     <t>F71</t>
@@ -1923,9 +1925,9 @@
     <t>• Micro Ingredients Astaxanthin 12mg (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Astaxantina Marina
-Microalga Roja
-Escudo Juvenil</t>
+    <t xml:space="preserve">Pispa Pink
+Nuara Tersa
+Garra Rojo</t>
   </si>
   <si>
     <t>F70</t>
@@ -1944,9 +1946,9 @@
     <t>• Megneta NAD+ Resveratrol 1200 mg Liposomal (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">NAD+ Resveratrol
-Uva Longeva
-Tiempo Detenido</t>
+    <t xml:space="preserve">Pispa Forever
+Nuara Atemporal
+Garra Tiempo</t>
   </si>
   <si>
     <t xml:space="preserve">• Péptidos de colágeno bovino tipo I y III 10-20 g por porción, o multi-tipo (I, II, III, V, X)
@@ -1987,9 +1989,9 @@
     <t>• Horbäach Nitric Oxide Beet Root Gummies (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Gomitas de Remolacha
-Corazón Rojo
-Pulso Vital</t>
+    <t xml:space="preserve">Pispa Red Gummies
+Nuara Rubí
+Garra Beet Gum</t>
   </si>
   <si>
     <t>F48</t>
@@ -2008,9 +2010,9 @@
 • B Life Omega 3 Aceite de Salmón (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Omega Corazón
-Mar Antártico
-Memoria y Corazón</t>
+    <t xml:space="preserve">Pispa Omega
+Nuara Marina
+Garra Ancla</t>
   </si>
   <si>
     <t>F38</t>
@@ -2034,9 +2036,9 @@
     <t>• VivoNu Cayenne Pepper Softgels (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Corazón Fuerte
-Espino Real
-Circulación Total</t>
+    <t xml:space="preserve">Pispa Heart
+Nuara Corazón
+Garra Latido</t>
   </si>
   <si>
     <t>F37</t>
@@ -2054,9 +2056,9 @@
     <t>• NEWELLME Beetroot Super Red Food Powder (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Remolacha en Polvo Activa
-Cosecha Roja
-Rendimiento Rojo</t>
+    <t xml:space="preserve">Pispa Red
+Nuara Torrente
+Garra Beet</t>
   </si>
   <si>
     <t>Defensas y vitaminas  ·  7 registros</t>
@@ -2080,9 +2082,9 @@
     <t>• Bella All Natural D3 K2 Drops Omega 3 MCT (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Gotas de Sol
-Sol Líquido
-Defensa Familiar</t>
+    <t xml:space="preserve">Pispa Sol Gotas
+Nuara Sol
+Garra Base</t>
   </si>
   <si>
     <t>F74</t>
@@ -2106,9 +2108,9 @@
     <t>• Hrvsta 20-Herb Blend Capsules (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Musgo Marino Veinte
-Veinte Hierbas
-Escudo Herbal</t>
+    <t xml:space="preserve">Pispa Sea Moss
+Nuara Escudo
+Garra Musgo</t>
   </si>
   <si>
     <t>F15</t>
@@ -2125,9 +2127,9 @@
 • Toyocare Vitamina D3 + K2 10.000 IU (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Hueso Fuerte D3+K2
-Luz Mediterránea
-Sol en Cápsula</t>
+    <t xml:space="preserve">Pispa Sol
+Nuara Solar
+Garra Rayo</t>
   </si>
   <si>
     <t>F54</t>
@@ -2146,9 +2148,9 @@
     <t>• Santa Cruz Paleo Zinc + Copper Caps (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Zinc y Cobre
-Mineral Ancestral
-Escudo Mineral</t>
+    <t xml:space="preserve">Pispa Zinc
+Nuara Cobre
+Garra Metal</t>
   </si>
   <si>
     <t>F56</t>
@@ -2169,9 +2171,9 @@
     <t>• Nature Made GLP-1 Companion Health Pack (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Compañero GLP-1
-Nutrición Consciente
-Respaldo Diario</t>
+    <t xml:space="preserve">Pispa Slim Care
+Nuara Compañera
+Garra Aliado</t>
   </si>
   <si>
     <t>F26</t>
@@ -2189,9 +2191,9 @@
     <t>• Toplux Moringa Capsules 1200mg (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Moringa Vital
-Hoja Verde Pura
-Energía del Campo</t>
+    <t xml:space="preserve">Pispa Green
+Nuara Verdor
+Garra Hoja</t>
   </si>
   <si>
     <t>F55</t>
@@ -2212,9 +2214,9 @@
     <t>• Rainbow Light Men's Multivitamin (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Hombre Activo
-Vitalidad Noble
-Energía Varonil</t>
+    <t xml:space="preserve">Pispa Man
+Nuara Hombre
+Garra Diario</t>
   </si>
   <si>
     <t>Cabello, piel y uñas  ·  6 registros</t>
@@ -2242,9 +2244,9 @@
 • MaryRuth's Daily Liquid Hair Formula (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Biotina Líquida Capilar
-Cabellera de Seda
-Melena Larga</t>
+    <t xml:space="preserve">Pispa Melena Drops
+Nuara Cascada
+Garra Crece</t>
   </si>
   <si>
     <t>F21</t>
@@ -2265,9 +2267,9 @@
     <t>• Bears with Benefits Biotin Gummies (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Gomitas Belleza Completa
-Jardín de Belleza
-Belleza Diaria</t>
+    <t xml:space="preserve">Pispa Glow Gummies
+Nuara Radiante
+Garra Facha</t>
   </si>
   <si>
     <t xml:space="preserve">• Bears with Benefits Biotin Gummies (EE. UU.)
@@ -2296,9 +2298,9 @@
     <t>• Clear Skin Acne Supplement (Clear-3) (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Piel Despejada
-Pureza Dérmica
-Cara Limpia</t>
+    <t xml:space="preserve">Pispa Clear
+Nuara Pura
+Garra Poro</t>
   </si>
   <si>
     <t>F52</t>
@@ -2319,9 +2321,9 @@
 • Josend MaxBiotin MultiVita (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Biotina Triple Belleza
-Seda Natural
-Melena Fuerte</t>
+    <t xml:space="preserve">Pispa Beauty
+Nuara Esplendor
+Garra Pinta</t>
   </si>
   <si>
     <t>F19</t>
@@ -2338,9 +2340,9 @@
     <t>• Megneta Complejo Avanzado Crecimiento del Cabello (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Fórmula Anticaída
-Bosque Capilar
-Cabello Abundante</t>
+    <t xml:space="preserve">Pispa Melena Max
+Nuara Raíz
+Garra Brote</t>
   </si>
   <si>
     <t>Potencia sexual masculina  ·  4 registros</t>
@@ -2371,9 +2373,9 @@
     <t>• Moshe Vitalidad Masculina 5 Tesoros (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Té Vigor Masculino
-Cinco Tesoros
-Hierro Varonil</t>
+    <t xml:space="preserve">Pispa Papi Té
+Nuara Tesoro
+Garra Cinco</t>
   </si>
   <si>
     <t>F58</t>
@@ -2395,9 +2397,9 @@
 • HiPlus Men's Testosterone Booster Power Complex (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Testosterona Natural
-Shilajit del Himalaya
-Potencia Máxima</t>
+    <t xml:space="preserve">Pispa Toro
+Nuara Varonil
+Garra Testo</t>
   </si>
   <si>
     <t>Gladiador: bebida potenciadora sexual masculina</t>
@@ -2429,9 +2431,9 @@
     <t>• Snap Prostate Health &amp; Nitric Oxide Chews (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Gomita Prostática
-Granada Real
-Vigor Nocturno</t>
+    <t xml:space="preserve">Pispa Papi Gummies
+Nuara Granada
+Garra Firme</t>
   </si>
   <si>
     <t>F61</t>
@@ -2451,9 +2453,9 @@
     <t>• Pumpkin Seed Oil + Saw Palmetto Softgel 1000mg (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Aceite de Calabaza
-Ahuyama Dorada
-Vejiga Tranquila</t>
+    <t xml:space="preserve">Pispa Don Calabaza
+Nuara Caudal
+Garra Flujo</t>
   </si>
   <si>
     <t>F60</t>
@@ -2475,9 +2477,9 @@
     <t>• Windboss Suplemento para Hombres (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Próstata Saludable
-Palma Enana
-Noches Completas</t>
+    <t xml:space="preserve">Pispa Don
+Nuara Plenitud
+Garra Prosta</t>
   </si>
   <si>
     <t>Cerebro y concentración  ·  2 registros</t>
@@ -2501,9 +2503,9 @@
 • Windboss Chicles/Mentas L-Teanina + B12 + B6 (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Menta Energizante
-Enfoque Puro
-Siempre Despierto</t>
+    <t xml:space="preserve">Pispa Boost
+Nuara Chispa
+Garra Mecha</t>
   </si>
   <si>
     <t>F81</t>
@@ -2521,9 +2523,9 @@
     <t>• Balincer Ginkgo Biloba (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ginkgo Memoria
-Árbol de la Memoria
-Mente Despierta</t>
+    <t xml:space="preserve">Pispa Focus
+Nuara Memoria
+Garra Mente</t>
   </si>
   <si>
     <t>Articulaciones y huesos  ·  3 registros</t>
@@ -2542,9 +2544,9 @@
     <t>• Airboy Vitamina D3 + K2 (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Vitamina Solar
-Sol de Mediodía
-Paso Firme</t>
+    <t xml:space="preserve">Pispa Sol Caps
+Nuara Soleada
+Garra Coraza</t>
   </si>
   <si>
     <t>F49</t>
@@ -2565,9 +2567,9 @@
     <t>• Balincer Calcium D3 K2 B12 Complex (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Calcio Articular
-Movimiento Libre
-Rodilla Sana</t>
+    <t xml:space="preserve">Pispa Flex
+Nuara Roble
+Garra Hueso</t>
   </si>
   <si>
     <t>F82</t>
@@ -2587,9 +2589,9 @@
     <t>• LOVING TREE Turmeric Curcumin Gummies (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cúrcuma Articular
-Oro de la India
-Rodillas Libres</t>
+    <t xml:space="preserve">Pispa Gold
+Nuara Soltura
+Garra Alivio</t>
   </si>
   <si>
     <t>Niños  ·  3 registros</t>
@@ -5486,7 +5488,7 @@
       <xdr:row>27</xdr:row>
       <xdr:rowOff>144750</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="21" name="Picture 21">
@@ -5996,7 +5998,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>36750</xdr:rowOff>
+      <xdr:rowOff>32000</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -8219,10 +8221,10 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>151500</xdr:rowOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>131250</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="16" name="Picture 16">
@@ -8258,8 +8260,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>63750</xdr:rowOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>151500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -8297,8 +8299,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>57000</xdr:rowOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>63750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -8336,8 +8338,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>43500</xdr:rowOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>57000</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -8375,8 +8377,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>40000</xdr:rowOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -8414,8 +8416,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>57000</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>40000</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -8453,7 +8455,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>57000</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
@@ -8492,8 +8494,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>63750</xdr:rowOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>57000</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -8531,8 +8533,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>43500</xdr:rowOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>63750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -8570,8 +8572,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>56999</xdr:rowOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -8609,8 +8611,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>43499</xdr:rowOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>56999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -8648,8 +8650,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>70499</xdr:rowOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -8687,8 +8689,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>43499</xdr:rowOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>70499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -8726,8 +8728,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>56999</xdr:rowOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -8765,8 +8767,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>56999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -8804,7 +8806,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
@@ -8843,7 +8845,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
@@ -8882,7 +8884,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
@@ -8921,7 +8923,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
@@ -8960,8 +8962,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>50249</xdr:rowOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -8999,7 +9001,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>50249</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
@@ -9038,8 +9040,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>56999</xdr:rowOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>50249</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -9077,8 +9079,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>43499</xdr:rowOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>56999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -9116,8 +9118,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -9155,7 +9157,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
@@ -9194,8 +9196,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>50249</xdr:rowOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -9233,8 +9235,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>50249</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -9272,7 +9274,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
@@ -9311,8 +9313,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>43499</xdr:rowOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -9350,7 +9352,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
@@ -9389,8 +9391,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>63749</xdr:rowOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -9428,8 +9430,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>50249</xdr:rowOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>63749</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -9467,8 +9469,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>63749</xdr:rowOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>50249</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -9506,8 +9508,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>56999</xdr:rowOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>63749</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -9545,8 +9547,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>56999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -9584,7 +9586,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>61</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
@@ -9623,7 +9625,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
@@ -9662,7 +9664,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>62</xdr:row>
       <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
@@ -9701,7 +9703,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>63</xdr:row>
       <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
@@ -9740,8 +9742,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>56999</xdr:rowOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -9779,8 +9781,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>56999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -9818,7 +9820,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
@@ -9857,7 +9859,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>69</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
@@ -9896,7 +9898,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
@@ -9935,8 +9937,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>50249</xdr:rowOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -9974,8 +9976,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>50249</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -10013,7 +10015,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
@@ -10052,8 +10054,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>50249</xdr:rowOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -10091,8 +10093,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>50249</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -10130,7 +10132,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>76</xdr:row>
       <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
@@ -10169,7 +10171,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
@@ -10208,7 +10210,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>79</xdr:row>
+      <xdr:row>78</xdr:row>
       <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
@@ -10247,7 +10249,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
@@ -10286,8 +10288,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>56999</xdr:rowOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -10325,8 +10327,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>56999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -10364,8 +10366,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>97499</xdr:rowOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -10403,8 +10405,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>50249</xdr:rowOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>97499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -10442,8 +10444,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>43499</xdr:rowOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>50249</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -10481,8 +10483,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -10520,8 +10522,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>83999</xdr:rowOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -10559,8 +10561,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>43499</xdr:rowOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>83999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -10598,8 +10600,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -10637,8 +10639,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>63749</xdr:rowOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -10676,8 +10678,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>151499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -10715,8 +10717,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>63749</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -10754,7 +10756,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>98</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
@@ -10793,7 +10795,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>99</xdr:row>
+      <xdr:row>96</xdr:row>
       <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
@@ -10832,7 +10834,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>101</xdr:row>
+      <xdr:row>98</xdr:row>
       <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
@@ -10871,7 +10873,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>102</xdr:row>
+      <xdr:row>99</xdr:row>
       <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
@@ -10910,7 +10912,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>103</xdr:row>
+      <xdr:row>101</xdr:row>
       <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
@@ -10949,8 +10951,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>105</xdr:row>
-      <xdr:rowOff>43499</xdr:rowOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -10988,7 +10990,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>107</xdr:row>
+      <xdr:row>103</xdr:row>
       <xdr:rowOff>39999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
@@ -11027,8 +11029,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
-      <xdr:row>109</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -11046,6 +11048,123 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId88" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>15600</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>83999</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1676400" cy="942975"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="89" name="Picture 89">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId89" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>15600</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>39999</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1676400" cy="942975"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="90" name="Picture 90">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId90" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>15600</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>39999</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1676400" cy="942975"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="91" name="Picture 91">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId91" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12008,7 +12127,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>36749</xdr:rowOff>
+      <xdr:rowOff>31999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -12047,7 +12166,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>36749</xdr:rowOff>
+      <xdr:rowOff>31999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -12086,7 +12205,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>36749</xdr:rowOff>
+      <xdr:rowOff>31999</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -18884,7 +19003,7 @@
       <c r="K11" s="26"/>
       <c r="L11" s="26"/>
     </row>
-    <row r="12" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
       <c r="B12" s="7" t="s">
         <v>1116</v>
@@ -26141,7 +26260,7 @@
       <c r="K34" s="26"/>
       <c r="L34" s="26"/>
     </row>
-    <row r="35" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="6"/>
       <c r="B35" s="7" t="s">
         <v>748</v>
@@ -26177,7 +26296,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="36" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="14"/>
       <c r="B36" s="15" t="s">
         <v>751</v>
@@ -26211,7 +26330,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="37" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="6"/>
       <c r="B37" s="7" t="s">
         <v>754</v>

--- a/salida/Productos_a_registrar_Guillermo.xlsx
+++ b/salida/Productos_a_registrar_Guillermo.xlsx
@@ -143,9 +143,9 @@
     <t>Septiembre 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Chill
-Nuara Armonía
-Garra Calm</t>
+    <t xml:space="preserve">Mocktisol: Tu mocktail contra la cara de cortisol
+Remanso: Baja el cortisol, sube la calma
+Tregua: Dale una tregua a tu cortisol</t>
   </si>
   <si>
     <t>C6</t>
@@ -177,9 +177,9 @@
 • Beyond Vitamins Aguaje + Fenogreco 1000 mg (México): 1.313 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Booty
-Nuara Silueta
-Garra Aguaje</t>
+    <t xml:space="preserve">Colita: Más colita, cero excusas
+Amazona: Curvas que vienen de la selva
+Guitarra: Cuerpo de guitarra, por fin</t>
   </si>
   <si>
     <t>F65</t>
@@ -217,9 +217,9 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Detox
-Nuara Dicha
-Garra Limpio</t>
+    <t xml:space="preserve">Jugosa: Sabor sandía, panza plana
+Serena: Calma tu panza y tus antojos
+Llenita: Llena, no inflada</t>
   </si>
   <si>
     <t>C2</t>
@@ -252,9 +252,9 @@
     <t>Últimos 28 días</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Kids Calm
-Nuara Cuento
-Garra Osito</t>
+    <t xml:space="preserve">Dormilón: El osito que los duerme
+Arrurrú: La canción de cuna en ositos
+Cobijita: Calma suavecita antes de dormir</t>
   </si>
   <si>
     <t>N6</t>
@@ -294,9 +294,9 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Papi Shot
-Nuara Gladiador
-Garra Toro</t>
+    <t xml:space="preserve">Centurión: Entra a la arena, sal invicto
+Maratón: La noche entera sin bajar el ritmo
+Anaconda: La bebida más grande del Amazonas</t>
   </si>
   <si>
     <t>C4</t>
@@ -326,9 +326,9 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Kids Focus
-Nuara Foco
-Garra Junior</t>
+    <t xml:space="preserve">Cerebrito: Gomitas para pequeños cerebritos
+Pupitre: Atentos en clase, felices en casa
+Brújula: Su atención, en la dirección correcta</t>
   </si>
   <si>
     <t>C5</t>
@@ -353,9 +353,9 @@
     <t>• Bcuelov Cayenne Pepper Supplement (EE. UU.):  u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Picante
-Nuara Cayena
-Garra Fuego</t>
+    <t xml:space="preserve">Ají: Ponle ají a tu metabolismo
+Ardiente: Calor que esculpe tu figura
+Diablo: Quema grasa como el diablo</t>
   </si>
   <si>
     <t>F39</t>
@@ -389,9 +389,9 @@
 • k2o Advanced Skin Hydration Mix (EE. UU.): 6.716 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Glow Shake
-Nuara Piel
-Garra Flex</t>
+    <t xml:space="preserve">Gelatina: Piel que tiembla de firme.
+Pradera: Colágeno de pastoreo, piel de verdad.
+Crack: El crack eres tú, no tu rodilla.</t>
   </si>
   <si>
     <t>F06</t>
@@ -426,9 +426,9 @@
 • NUTRAHARMONY Biotin Gummies Sugar (EE. UU.): 515 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Melena
-Nuara Cabellera
-Garra Tupido</t>
+    <t xml:space="preserve">Moño: Moño gordo, almohada sin pelos.
+Arraigo: Tu pelo se queda donde está.
+Retoño: Después del parto, tu pelo vuelve.</t>
   </si>
   <si>
     <t>N4</t>
@@ -457,9 +457,9 @@
 • Lemme Sleep Gummies with 5mg Melatonin, Magnesium, L (EE. UU.): 1.300 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Sleep
-Nuara Sueño
-Garra Noche</t>
+    <t xml:space="preserve">Privado: Te deja privado toda la noche
+Lirón: Duerme como un lirón, sin despertar
+Seguidito: Toda la noche, seguidito</t>
   </si>
   <si>
     <t>N1</t>
@@ -486,9 +486,9 @@
 • First Day Kids Calming Magnesium Gummies Ages 4 (EE. UU.): 288 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Kids Calm Gotas
-Nuara Nana
-Garra Mini</t>
+    <t xml:space="preserve">Ronrón: Calmaditos como un gatico
+Abrazo: Calma como un abrazo de mamá
+Quietico: Unas gotitas y quietico</t>
   </si>
   <si>
     <t>N5</t>
@@ -522,9 +522,9 @@
 • Gardenika Organic Laxative Loose Leaf Tea, Caffeine (EE. UU.): 15 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Fluye Té
-Nuara Alivio
-Garra Libre</t>
+    <t xml:space="preserve">Corre: Tómatelo y corre al baño
+Amanece: Tómalo de noche, amanece ligera
+Destape: Destapa la tubería sin pena</t>
   </si>
   <si>
     <t>N3</t>
@@ -552,9 +552,9 @@
 • $1 AUCTIONS Soursop Sleep Drops with Melatonin 5mg, Ashwagandha &amp; L (EE. UU.): 13 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Sleep Gotas
-Nuara Luna
-Garra Off</t>
+    <t xml:space="preserve">Modo Avión: Unas gotas y modo avión
+Somnia: Tu noche empieza en una gota
+Apagón: Veinte minutos y apagón</t>
   </si>
   <si>
     <t>N2</t>
@@ -578,9 +578,9 @@
 • UPMER Pack Magnesio 7 en 1 + Omega 3 (México): 3.051 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Magnesio
-Nuara Reposo
-Garra Mag</t>
+    <t xml:space="preserve">Doce: Doce formas de magnesio, una noche
+Fondo: Entrena a fondo, duerme a fondo
+Bostezo: Si bostezaste, ya sabes</t>
   </si>
   <si>
     <t>F01</t>
@@ -610,9 +610,9 @@
 • Vital Source Feminine Balance Gummies (EE. UU.): 10.985 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Miau
-Nuara Íntima
-Garra Flora</t>
+    <t xml:space="preserve">Cuqui: Tu cuqui, fresquita todo el día
+pHlora: Tu pH en equilibrio, naturalmente
+Melosa: Fresca, dulce y sin pena</t>
   </si>
   <si>
     <t>F02</t>
@@ -632,9 +632,9 @@
 • LeeFar Cutting Drops Lymphatic Debloat (EE. UU.): 15.488 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Drena Gotas
-Nuara Fluida
-Garra Desinfla Gotas</t>
+    <t xml:space="preserve">Linfi: Deshincha tu cara cada mañana
+Ondina: Deja que el agua se vaya
+Sculpta: Esculpe tu postoperatorio</t>
   </si>
   <si>
     <t>F09</t>
@@ -661,9 +661,9 @@
 • NeoCell Creatine Monohydrate + Multi Collagen (EE. UU.): 11.436 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Power
-Nuara Curva
-Garra Glute</t>
+    <t xml:space="preserve">Pompi: Más pompi, menos excusas
+Curvé: Curvas firmes, piel de seda
+Squatta: Hecha para el día de pierna</t>
   </si>
   <si>
     <t>F04</t>
@@ -687,9 +687,9 @@
 • Windboss Hack your Tummy (paquete) (México): 14.245 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Pancita
-Nuara Ligera
-Garra Gut</t>
+    <t xml:space="preserve">Tummy: Panza plana, cero pedos
+Simbio: Tu flora, en perfecta armonía
+Tripa: Come duro, sin inflarte</t>
   </si>
   <si>
     <t>F03</t>
@@ -710,9 +710,9 @@
 • HS Hero Sport Creatina Monohidratada 650 g (México): 1.209 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Power Pura
-Nuara Fuerza
-Garra Crea</t>
+    <t xml:space="preserve">Brava: Ella también levanta pesado
+Kreo: Creatina pura. Nada más.
+Tanke: Llena el tanque, rompe tu récord</t>
   </si>
   <si>
     <t>F05</t>
@@ -732,9 +732,9 @@
 • Toplux Organic Beet Root Capsules (EE. UU.): 18.180 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Firme
-Nuara Vigor
-Garra Pump</t>
+    <t xml:space="preserve">Tieso: Firme cuando toca
+Novios: Como cuando eran novios
+Vena: Bombea sangre, bombea todo</t>
   </si>
   <si>
     <t>F11</t>
@@ -770,9 +770,9 @@
 • Toyocare Bebida relajante Ashwagandha KSM-66 (México): 1.565 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Relax
-Nuara Ocaso
-Garra Chill</t>
+    <t xml:space="preserve">Pijamada: Tu sleepy girl mocktail en polvo
+Velada: Cierra el día con tu velada
+Pitazo: Sonó el pitazo: se acabó el día</t>
   </si>
   <si>
     <t>F07</t>
@@ -798,9 +798,9 @@
 • SWIYIE Complejo de Colágeno Múltiple (120 cápsulas) (México): 6.545 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Glow
-Nuara Lozana
-Garra Piel</t>
+    <t xml:space="preserve">Dewy: Piel de rocío, pelo de comercial.
+Quinta: Cinco colágenos, una sola rutina.
+Todita: Pa' que te veas todita divina.</t>
   </si>
   <si>
     <t>F08</t>
@@ -818,9 +818,9 @@
     <t>• Vitafusion Fiber Well Sugar Free Gummies (EE. UU.): 38.736 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Fluye
-Nuara Ritmo
-Garra Fibra</t>
+    <t xml:space="preserve">Popi: Tu popó diario, sin drama
+Puntual: Tu intestino, siempre puntual
+Trono: Tu cita diaria con el trono</t>
   </si>
   <si>
     <t>F40</t>
@@ -846,9 +846,9 @@
 • VEV DeepCalm Magnesium Complex Gummies 14-in-1 (EE. UU.): 18.378 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Mimir
-Nuara Arrullo
-Garra Rest</t>
+    <t xml:space="preserve">Pestañita: Échate una pestañita de verdad
+Plácida: Duerme suave, despierta ligera
+Nube: Tu mente, en modo nube</t>
   </si>
   <si>
     <t>F16</t>
@@ -869,9 +869,9 @@
     <t>• Toplux Organic Beet Root Tablets 2040mg (EE. UU.): 22.673 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Red Tabs
-Nuara Pulso
-Garra Bombeo</t>
+    <t xml:space="preserve">Sístole: La presión en su punto
+Carmín: Rojo natural para tu corazón
+Cucho: Pa' que el cucho dure</t>
   </si>
   <si>
     <t>F35</t>
@@ -893,9 +893,9 @@
     <t>• Windboss Combo Cortisol + Myo-Inositol (kit 2 frascos) (México): 28.383 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Cortisol
-Nuara Calma
-Garra Temple</t>
+    <t xml:space="preserve">Avispa: Cintura de avispa, cortisol abajo
+Inosa: Hormonas en calma, cortisol abajo
+Cortizero: Cortisol a cero, abdomen en serio</t>
   </si>
   <si>
     <t>F14</t>
@@ -913,9 +913,9 @@
     <t>• Body Magic Chlorophyll Pill (EE. UU.): 19.913 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Fresh
-Nuara Fresca
-Garra Verde</t>
+    <t xml:space="preserve">Rica: Huele rico, de adentro hacia afuera
+Clora: Pureza verde que se nota
+Fresco: Suda tranquilo, mantente fresco</t>
   </si>
   <si>
     <t>F72</t>
@@ -946,9 +946,9 @@
 • Windboss Cápsulas de Vitalidad y Resistencia 2026 (México): 1.588 u.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Papi
-Nuara Potencia
-Garra Rey</t>
+    <t xml:space="preserve">Semental: Listo pa' la faena, toda la noche
+Bestia: Testosterona de bestia, en cama y gym
+Caballero: Discreto afuera, fiera adentro</t>
   </si>
   <si>
     <t>F24</t>
@@ -1027,9 +1027,9 @@
     <t>• YESNAP Lymphatic Drainage Support 12-in-1 (30 sticks, naranja-mango) (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Drena Stick
-Nuara Cauce
-Garra Seco</t>
+    <t xml:space="preserve">Plof: Échalo al agua y plof
+Marea: Suelta lo que retienes
+Lunes: Deshincha el finde en un día</t>
   </si>
   <si>
     <t>F27</t>
@@ -1049,9 +1049,9 @@
 • Micro Ingredients Oregano Oil with Black Seed Oil (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Orégano
-Nuara Guardiana
-Garra Escudo</t>
+    <t xml:space="preserve">Chao Bichos: Limpieza intestinal que sí se siente
+Baraka: La semilla bendita de los ancestros
+Fortín: Defensas blindadas para toda la casa</t>
   </si>
   <si>
     <t>F76</t>
@@ -1069,9 +1069,9 @@
     <t>• Bella All Natural Colon Cleanse 400g (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Papaya
-Nuara Limpia
-Garra Reset</t>
+    <t xml:space="preserve">Dame Papaya: Aquí sí puedes dar papaya
+Carica: La hoja verde que limpia
+Escoba: Barre el colon de una</t>
   </si>
   <si>
     <t>F80</t>
@@ -1089,9 +1089,9 @@
     <t>• Nutricost NAC N-Acetyl L-Cysteine Capsules (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Respira
-Nuara Respiro
-Garra Filtro</t>
+    <t xml:space="preserve">Rumbera: Rumbea hoy, amanece divina mañana
+Nácar: Brilla limpia por dentro
+Bocanada: Respira hondo otra vez</t>
   </si>
   <si>
     <t>F77</t>
@@ -1112,9 +1112,9 @@
     <t>• Milamiamor 15 Day Cleanse (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Reset
-Nuara Reinicio
-Garra Purga</t>
+    <t xml:space="preserve">Quince: Panza plana en 15 días
+Templo: Limpia tu templo por dentro
+Santo Remedio: El remedio de la abuela, en cápsula</t>
   </si>
   <si>
     <t>F50</t>
@@ -1141,9 +1141,9 @@
     <t>• ATRAKT D-BLOAT Advanced Debloat Powder (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Planita
-Nuara Vientre
-Garra Flat</t>
+    <t xml:space="preserve">Cinturita: Cinturita de avispa en un vaso
+Pluma: Ligera como una pluma
+Marcado: Bota el agua, marca el abdomen</t>
   </si>
   <si>
     <t>F31</t>
@@ -1162,9 +1162,9 @@
     <t>• BioGaia Fresh Breath Oral Probiotics (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Besito
-Nuara Aliento
-Garra Fresh</t>
+    <t xml:space="preserve">Besable: Aliento listo para besar
+Suspiro: Frescura que viene de adentro
+Labia: Háblale de cerquita</t>
   </si>
   <si>
     <t>F73</t>
@@ -1182,9 +1182,9 @@
     <t>• Horbäach Liquid Chlorophyll Drops (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Fresh Gotas
-Nuara Rocío
-Garra Verde Gotas</t>
+    <t xml:space="preserve">Verdi: Tu agua verde de cada día
+Esmeralda: La joya verde de Colombia
+Coqueta: Fresquita donde más importa</t>
   </si>
   <si>
     <t>F33</t>
@@ -1200,9 +1200,9 @@
 • MVPCARE Desintoxicación Linfática (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Drena
-Nuara Liviana
-Garra Desinfla</t>
+    <t xml:space="preserve">Splash: Suelta el agua, luce el cuerpo
+Manantial: 27 plantas que abren el manantial
+Tacón: Todo el día en tacón, sin hinchazón</t>
   </si>
   <si>
     <t xml:space="preserve">• LeafLea Senna Tea Bags (EE. UU.)
@@ -1263,9 +1263,9 @@
     <t>• Loosey Goosey Calming Pouches 3 Pack (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Calma
-Nuara Pausa
-Garra Frío</t>
+    <t xml:space="preserve">Tranqui: Ponte una y tranqui
+Sutil: Calma discreta, en tu bolsillo
+Hielo: Hielo en las venas, sin nicotina</t>
   </si>
   <si>
     <t>F43</t>
@@ -1290,9 +1290,9 @@
     <t>• Windboss Ashwagandha KSM-66 + L-Teanina + PS (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Zen
-Nuara Sosiego
-Garra Aplomo</t>
+    <t xml:space="preserve">Relajao: Vive relajao, aunque el mundo no
+Exhala: Inhala calma, exhala cortisol
+Estoico: Lo que no controlas, no te estresa</t>
   </si>
   <si>
     <t xml:space="preserve">• Project Superhuman DreamOn Sleep Gummies for Adult Men &amp; Women, 8 (EE. UU.)
@@ -1348,9 +1348,9 @@
 • Wellah Electrolytes Sample Pack + Shaker (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Suero
-Nuara Oasis
-Garra Hidra</t>
+    <t xml:space="preserve">Glup: Hidrátate de un solo glup
+Brisa: Hidratación fresca como brisa de mar
+Voltio: Recarga tus músculos al instante</t>
   </si>
   <si>
     <t>F68</t>
@@ -1373,9 +1373,9 @@
 • Windboss NAD+ Liposomal NR 900 mg (100 cápsulas) (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Young
-Nuara Longeva
-Garra Cell</t>
+    <t xml:space="preserve">Rewind: Rebobina tu edad
+Perenne: Más años, con más vida
+Mito: Energía desde tus mitocondrias</t>
   </si>
   <si>
     <t>F20</t>
@@ -1401,9 +1401,9 @@
 • Montue Gotitas B12 + B6 (40 porciones, frambuesa) (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Pila
-Nuara Despierta
-Garra Boost</t>
+    <t xml:space="preserve">Enchufe: Enchúfate en segundos
+Candela: Energía cálida que no se apaga
+Lúcido: Mente clara, cero bajón</t>
   </si>
   <si>
     <t>F28</t>
@@ -1419,9 +1419,9 @@
 • Vital Source Creatine Gummies (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Power Gummies
-Nuara Tono
-Garra Crea Gum</t>
+    <t xml:space="preserve">Fuercita: Tu dosis diaria de fuercita
+Tonus: Firme y fuerte, todos los días
+Colmillo: Muerde fuerte, levanta más</t>
   </si>
   <si>
     <t>F22</t>
@@ -1439,9 +1439,9 @@
     <t>• BODYHEALTH Perfect Amino Tablets (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Amino
-Nuara Esencial
-Garra Recarga</t>
+    <t xml:space="preserve">Amina: Recupérate como nueva
+Ocho: Los 8 que tu músculo necesita
+Forja: El músculo se forja serie a serie</t>
   </si>
   <si>
     <t>F23</t>
@@ -1463,9 +1463,9 @@
 • Euphoric 100% Whey Protein + Creatina (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Protein
-Nuara Esculpida
-Garra Whey</t>
+    <t xml:space="preserve">Agüita: Proteína que parece agüita
+Satín: Músculo firme, piel de satín
+Masa: Saca masa de verdad</t>
   </si>
   <si>
     <t>F69</t>
@@ -1480,9 +1480,9 @@
     <t>• Cata-Kor NMN Powder 1000 mg (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Young Drink
-Nuara Aurora
-Garra Motor</t>
+    <t xml:space="preserve">Veinte: Siéntete de veinte otra vez
+Eon: Tus células no tienen edad
+Pistón: Tus células a todo pistón</t>
   </si>
   <si>
     <t>F59</t>
@@ -1502,9 +1502,9 @@
     <t>• Toyocare palitos de miel con shilajit (30 unidades) (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Honey
-Nuara Brío
-Garra Roca</t>
+    <t xml:space="preserve">Garañón: Para cumplir como un garañón
+Lunamiel: La luna de miel nunca termina
+Himal: La fuerza del Himalaya, discreta</t>
   </si>
   <si>
     <t>Salud íntima y libido femenina  ·  6 registros</t>
@@ -1537,9 +1537,9 @@
 • VivoNu Probióticos para la Mujer con Arándano (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Arándano
-Nuara Flora
-Garra Berry</t>
+    <t xml:space="preserve">Berry Babe: Adiós ardor, hola berry babe
+Cranelle: Flora íntima y vías urinarias protegidas
+Blindada: Chao infecciones, ahí abajo mandas tú</t>
   </si>
   <si>
     <t>F63</t>
@@ -1564,9 +1564,9 @@
     <t>• Adapto Drive Maca Root Drops (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Fuego
-Nuara Deseo
-Garra Ganas</t>
+    <t xml:space="preserve">Antojada: Unas gotitas y quedas antojada
+Fuego Lento: Enciende tu deseo, despacito
+Prendida: A los cuarenta, más prendida que nunca</t>
   </si>
   <si>
     <t>F45</t>
@@ -1589,9 +1589,9 @@
     <t>• Nello Superbalance Hormonal Support Drink Mix (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Balance
-Nuara Equilibrio
-Garra Ella</t>
+    <t xml:space="preserve">Sin Drama: Tus hormonas en paz, tú también
+Selene: Fluye con tu ciclo, como la luna
+Cien Maridos: La raíz que equilibra a cualquiera</t>
   </si>
   <si>
     <t>F44</t>
@@ -1611,9 +1611,9 @@
 • Zesty Pro Inositol 200 g + Pink Fury 100 g (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Hormonita
-Nuara Ciclo
-Garra Ritmo</t>
+    <t xml:space="preserve">Ovy: Ovarios felices, tú también
+Exacta: Tu regla, exacta otra vez
+Cigüeña: Prepara tus ovarios para la cigüeña</t>
   </si>
   <si>
     <t>F64</t>
@@ -1633,9 +1633,9 @@
     <t>• Montue Maca &amp; Fenogreco Gummies Combo (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Curvas
-Nuara Diosa
-Garra Curva</t>
+    <t xml:space="preserve">Rebote: Que rebote todo, hasta las ganas
+Mamacita: Curvas que hacen voltear cabezas
+Sabrosa: Más curvas, más deseo</t>
   </si>
   <si>
     <t>Quemar grasa y bajar de peso  ·  8 registros</t>
@@ -1662,9 +1662,9 @@
     <t>• Apothékary Blue Burn Metabolic Support Drops (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Slim Gotas
-Nuara Templanza
-Garra Cut</t>
+    <t xml:space="preserve">Azulejo: Una gota azul y chao antojo
+Mantra: El antojo pasa, tú no
+Pico Cerrado: Pico cerrado, nevera cerrada</t>
   </si>
   <si>
     <t>F79</t>
@@ -1685,9 +1685,9 @@
     <t>• Coleology Cutting Jelly (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Jelly
-Nuara Saciada
-Garra Full</t>
+    <t xml:space="preserve">Chupi: Chúpalo y chao hambre
+Gelée: Llena por dentro, linda por fuera
+Matahambre: Mata el hambre entre comidas</t>
   </si>
   <si>
     <t>F34</t>
@@ -1706,9 +1706,9 @@
     <t>• Yesnap MOCKTALE-1 Metabolic Drink Mix (30 sobres) (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Slim
-Nuara Mesura
-Garra Lean</t>
+    <t xml:space="preserve">Mute: Silencia el antojo
+Bioma: Tu intestino manda, tu cuerpo responde
+Botón: Que el botón del pantalón respire</t>
   </si>
   <si>
     <t>F42</t>
@@ -1731,9 +1731,9 @@
     <t>• Blood Sugar Complex 20 Vitamins &amp; Minerals (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Glucosa
-Nuara Balance
-Garra Nivel</t>
+    <t xml:space="preserve">Insu: Chao picos de azúcar
+Amarga: Lo amargo que te endulza
+Timón: Usted maneja su azúcar</t>
   </si>
   <si>
     <t>F13</t>
@@ -1756,9 +1756,9 @@
 • Multiblue Berberina HCl con Canela y Cúrcuma (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Berberina
-Nuara Esbelta
-Garra Freno</t>
+    <t xml:space="preserve">Tallita: Una talla menos, sin bisturí
+Ceilán: Especias de oro para tu metabolismo
+Tumbapanza: Pa' tumbar la panza</t>
   </si>
   <si>
     <t>F10</t>
@@ -1787,9 +1787,9 @@
     <t>• Leefar Cutting Bundle (Cutting Mix + Cutting Drops) (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Burn Drink
-Nuara Contorno
-Garra Shred</t>
+    <t xml:space="preserve">Mañanera: La que te quema temprano
+Yerbal: El mate que afina tu figura
+Sauna: Suda como en el sauna</t>
   </si>
   <si>
     <t>F41</t>
@@ -1810,9 +1810,9 @@
     <t>• Toplux Keto Burn (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Burn
-Nuara Brasa
-Garra Quema</t>
+    <t xml:space="preserve">Ketty: Keto sin sufrir
+Irvinga: El secreto africano del mango
+Termita: Se come tu grasa</t>
   </si>
   <si>
     <t>F12</t>
@@ -1834,9 +1834,9 @@
     <t>• Montue Gomitas de ACV (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Manzanita
-Nuara Manzana
-Garra Apple</t>
+    <t xml:space="preserve">Mordisco: Un mordisco y chao antojo
+Huerta: Del huerto a tu cintura
+Brindis: El brindis que sí adelgaza</t>
   </si>
   <si>
     <t>Colágeno y antiedad  ·  7 registros</t>
@@ -1863,9 +1863,9 @@
     <t>• Cymbiotika Liposomal Glutathione (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Bright Shot
-Nuara Luz
-Garra Glow</t>
+    <t xml:space="preserve">Glassy: Piel de vidrio en un sorbo.
+Porcelana: Piel de porcelana, sin una mancha.
+Lechita: Piel de leche, manchas pa' fuera.</t>
   </si>
   <si>
     <t>F25</t>
@@ -1888,9 +1888,9 @@
 • Cata-Kor Liposomal Glutathione 1155 mg (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Bright
-Nuara Luminosa
-Garra Parejo</t>
+    <t xml:space="preserve">Borrón: Borrón y piel nueva.
+Lienzo: Tu piel, un lienzo uniforme.
+Camello: Camella al sol, sin quedar manchado.</t>
   </si>
   <si>
     <t>F51</t>
@@ -1905,9 +1905,9 @@
     <t>• Youtheory Collagen Liquid 5,000 mg (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Glow Shot
-Nuara Firme
-Garra Joint</t>
+    <t xml:space="preserve">Boing: Piel que rebota, en un shot.
+Cisne: Cuello firme, porte de cisne.
+Bisagra: Rodillas aceitadas, cero chirridos.</t>
   </si>
   <si>
     <t>F71</t>
@@ -1925,9 +1925,9 @@
     <t>• Micro Ingredients Astaxanthin 12mg (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Pink
-Nuara Tersa
-Garra Rojo</t>
+    <t xml:space="preserve">Flaminga: El secreto rosado del flamenco.
+Rubra: La microalga roja de la juventud.
+Salmón: Recupérate como salmón contracorriente.</t>
   </si>
   <si>
     <t>F70</t>
@@ -1946,9 +1946,9 @@
     <t>• Megneta NAD+ Resveratrol 1200 mg Liposomal (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Forever
-Nuara Atemporal
-Garra Tiempo</t>
+    <t xml:space="preserve">Batería: Batería al cien, edad en pausa.
+Siempreviva: La flor que nunca se marchita.
+Cronos: Tú mandas sobre el tiempo.</t>
   </si>
   <si>
     <t xml:space="preserve">• Péptidos de colágeno bovino tipo I y III 10-20 g por porción, o multi-tipo (I, II, III, V, X)
@@ -1989,9 +1989,9 @@
     <t>• Horbäach Nitric Oxide Beet Root Gummies (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Red Gummies
-Nuara Rubí
-Garra Beet Gum</t>
+    <t xml:space="preserve">Chapetas: Chapetas de pura energía
+Burdeos: Rojo vino, energía sin resaca
+Remo: Rema más, cánsate menos</t>
   </si>
   <si>
     <t>F48</t>
@@ -2010,9 +2010,9 @@
 • B Life Omega 3 Aceite de Salmón (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Omega
-Nuara Marina
-Garra Ancla</t>
+    <t xml:space="preserve">Sardi: Pescadito pa' la cabeza
+Austral: Puro mar del sur
+Pez Gordo: Cabeza y corazón de jefe</t>
   </si>
   <si>
     <t>F38</t>
@@ -2036,9 +2036,9 @@
     <t>• VivoNu Cayenne Pepper Softgels (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Heart
-Nuara Corazón
-Garra Latido</t>
+    <t xml:space="preserve">Riego: Que la sangre llegue a todo
+Cordial: La flor que cuida tu corazón
+Calentura: Pica, prende y circula</t>
   </si>
   <si>
     <t>F37</t>
@@ -2056,9 +2056,9 @@
     <t>• NEWELLME Beetroot Super Red Food Powder (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Red
-Nuara Torrente
-Garra Beet</t>
+    <t xml:space="preserve">Fucsia: El batido que te prende
+Terciopelo: Tu red velvet natural
+Escarabajo: Pa' subir como escarabajo</t>
   </si>
   <si>
     <t>Defensas y vitaminas  ·  7 registros</t>
@@ -2082,9 +2082,9 @@
     <t>• Bella All Natural D3 K2 Drops Omega 3 MCT (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Sol Gotas
-Nuara Sol
-Garra Base</t>
+    <t xml:space="preserve">Sunnie: Tu gotita de sol diaria
+Albora: Del alba a la luna, huesos fuertes
+Pilar: Tus huesos sostienen tu vida</t>
   </si>
   <si>
     <t>F74</t>
@@ -2108,9 +2108,9 @@
     <t>• Hrvsta 20-Herb Blend Capsules (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Sea Moss
-Nuara Escudo
-Garra Musgo</t>
+    <t xml:space="preserve">Sirena: Musgo marino para sirenas imparables
+Herbaria: Veinte plantas, una defensa sabia
+Tótem: Fuerza ancestral, defensas de guerrero</t>
   </si>
   <si>
     <t>F15</t>
@@ -2127,9 +2127,9 @@
 • Toyocare Vitamina D3 + K2 10.000 IU (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Sol
-Nuara Solar
-Garra Rayo</t>
+    <t xml:space="preserve">Rayito: Sol en cápsula para días grises
+Lumbre: La luz dorada de tus huesos
+Titanio: Huesos de titanio, cero lesiones</t>
   </si>
   <si>
     <t>F54</t>
@@ -2148,9 +2148,9 @@
     <t>• Santa Cruz Paleo Zinc + Copper Caps (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Zinc
-Nuara Cobre
-Garra Metal</t>
+    <t xml:space="preserve">Carita: Chao granitos, hola pelo brillante
+Zinnia: Belleza que florece desde adentro
+Cresta: Pelo y defensas en la cresta</t>
   </si>
   <si>
     <t>F56</t>
@@ -2171,9 +2171,9 @@
     <t>• Nature Made GLP-1 Companion Health Pack (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Slim Care
-Nuara Compañera
-Garra Aliado</t>
+    <t xml:space="preserve">Flaquis: Flaquis, pero con pelo y energía
+Cómplice: Pierde peso, no tu brillo
+Solo Kilos: Bajas kilos, no músculo ni pelo</t>
   </si>
   <si>
     <t>F26</t>
@@ -2191,9 +2191,9 @@
     <t>• Toplux Moringa Capsules 1200mg (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Green
-Nuara Verdor
-Garra Hoja</t>
+    <t xml:space="preserve">Mori: Energía verde sin taquicardia
+Oleifera: El árbol milagro, en su forma pura
+Matica: La matica que da energía</t>
   </si>
   <si>
     <t>F55</t>
@@ -2214,9 +2214,9 @@
     <t>• Rainbow Light Men's Multivitamin (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Man
-Nuara Hombre
-Garra Diario</t>
+    <t xml:space="preserve">Machete: Afilado de las 5 a.m. a medianoche
+Mando: Energía para tomar el mando
+Parce: El multi de tu parce</t>
   </si>
   <si>
     <t>Cabello, piel y uñas  ·  6 registros</t>
@@ -2244,9 +2244,9 @@
 • MaryRuth's Daily Liquid Hair Formula (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Melena Drops
-Nuara Cascada
-Garra Crece</t>
+    <t xml:space="preserve">Flip: Pelo largo pa'l hair flip.
+Semilla: Siembra hoy, melena mañana.
+Pelazo: Qué pelazo, parce.</t>
   </si>
   <si>
     <t>F21</t>
@@ -2267,9 +2267,9 @@
     <t>• Bears with Benefits Biotin Gummies (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Glow Gummies
-Nuara Radiante
-Garra Facha</t>
+    <t xml:space="preserve">Lindura: Lindura de pelo, piel y uñas.
+Pétalo: Belleza suave, de adentro hacia afuera.
+Esmalte: Uñas que no se quiebran.</t>
   </si>
   <si>
     <t xml:space="preserve">• Bears with Benefits Biotin Gummies (EE. UU.)
@@ -2298,9 +2298,9 @@
     <t>• Clear Skin Acne Supplement (Clear-3) (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Clear
-Nuara Pura
-Garra Poro</t>
+    <t xml:space="preserve">Barrida: Le barre los barros.
+Órbita: Tu piel en paz, todo el ciclo.
+Liso: Cara lisa, actitud lisa.</t>
   </si>
   <si>
     <t>F52</t>
@@ -2321,9 +2321,9 @@
 • Josend MaxBiotin MultiVita (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Beauty
-Nuara Esplendor
-Garra Pinta</t>
+    <t xml:space="preserve">Escarcha: Pelo con escarcha, uñas de acero.
+Velvet: Pelo de terciopelo, piel de seda.
+Cuarentona: Cuarentona y más divina que nunca.</t>
   </si>
   <si>
     <t>F19</t>
@@ -2340,9 +2340,9 @@
     <t>• Megneta Complejo Avanzado Crecimiento del Cabello (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Melena Max
-Nuara Raíz
-Garra Brote</t>
+    <t xml:space="preserve">Trenza: Trenza hasta la cintura.
+Frondosa: Volumen que viene de la naturaleza.
+Copete: Copete firme, entradas en retirada.</t>
   </si>
   <si>
     <t>Potencia sexual masculina  ·  4 registros</t>
@@ -2373,9 +2373,9 @@
     <t>• Moshe Vitalidad Masculina 5 Tesoros (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Papi Té
-Nuara Tesoro
-Garra Cinco</t>
+    <t xml:space="preserve">Dragón: Cinco tesoros, fuego de dragón
+Té Quiero: Una taza y te quiero toda
+Viejo Verde: Más años, más ganas</t>
   </si>
   <si>
     <t>F58</t>
@@ -2397,9 +2397,9 @@
 • HiPlus Men's Testosterone Booster Power Complex (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Toro
-Nuara Varonil
-Garra Testo</t>
+    <t xml:space="preserve">Piedra: Duro como piedra, toda la noche
+Sherpa: Aguante de alta montaña
+Ébano: Vigor negro, discreto y potente</t>
   </si>
   <si>
     <t>Gladiador: bebida potenciadora sexual masculina</t>
@@ -2431,9 +2431,9 @@
     <t>• Snap Prostate Health &amp; Nitric Oxide Chews (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Papi Gummies
-Nuara Granada
-Garra Firme</t>
+    <t xml:space="preserve">Coronel: El coronel sigue en pie
+Volcán: Vigor que hace erupción
+Todavía: Todavía funciona, y con ganas</t>
   </si>
   <si>
     <t>F61</t>
@@ -2453,9 +2453,9 @@
     <t>• Pumpkin Seed Oil + Saw Palmetto Softgel 1000mg (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Don Calabaza
-Nuara Caudal
-Garra Flujo</t>
+    <t xml:space="preserve">Chorro: Orina como a los veinte
+Ahuyama: La pepa que cuida tu próstata
+Sereno: Noches sin levantarte al baño</t>
   </si>
   <si>
     <t>F60</t>
@@ -2477,9 +2477,9 @@
     <t>• Windboss Suplemento para Hombres (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Don
-Nuara Plenitud
-Garra Prosta</t>
+    <t xml:space="preserve">Patriarca: Manda en casa, rinde en la cama
+Zincero: Próstata sana, hombre zincero
+Pipí Feliz: Sin ardor, sin pausas, sin vergüenza</t>
   </si>
   <si>
     <t>Cerebro y concentración  ·  2 registros</t>
@@ -2503,9 +2503,9 @@
 • Windboss Chicles/Mentas L-Teanina + B12 + B6 (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Boost
-Nuara Chispa
-Garra Mecha</t>
+    <t xml:space="preserve">Despabila: Un chicle y te despabilas
+Nítido: Enfoque nítido, sin nervios
+Clutch: Energía para el momento clutch</t>
   </si>
   <si>
     <t>F81</t>
@@ -2523,9 +2523,9 @@
     <t>• Balincer Ginkgo Biloba (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Focus
-Nuara Memoria
-Garra Mente</t>
+    <t xml:space="preserve">Acordeón: El único acordeón permitido
+Evoca: Tus recuerdos, siempre a la mano
+Filo: Mente con filo, siempre</t>
   </si>
   <si>
     <t>Articulaciones y huesos  ·  3 registros</t>
@@ -2544,9 +2544,9 @@
     <t>• Airboy Vitamina D3 + K2 (México)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Sol Caps
-Nuara Soleada
-Garra Coraza</t>
+    <t xml:space="preserve">Solecito: Tu dosis diaria de sol
+Perla: Huesos firmes, belleza que permanece
+Atlas: Huesos que cargan con todo</t>
   </si>
   <si>
     <t>F49</t>
@@ -2567,9 +2567,9 @@
     <t>• Balincer Calcium D3 K2 B12 Complex (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Flex
-Nuara Roble
-Garra Hueso</t>
+    <t xml:space="preserve">Bailao: Pa' seguir bailando sin dolor
+Ágil: Moverte libre a cualquier edad
+Acero: Rodillas de acero, sin crujidos</t>
   </si>
   <si>
     <t>F82</t>
@@ -2589,9 +2589,9 @@
     <t>• LOVING TREE Turmeric Curcumin Gummies (EE. UU.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pispa Gold
-Nuara Soltura
-Garra Alivio</t>
+    <t xml:space="preserve">Doradita: Desinflama rico, gomita a gomita
+Haldi: El ritual dorado de la India
+Bombero: Apaga el fuego de tus articulaciones</t>
   </si>
   <si>
     <t>Niños  ·  3 registros</t>
@@ -5842,7 +5842,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -5881,7 +5881,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -5920,7 +5920,1236 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>36750</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>36750</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>36749</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>36749</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>36749</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>32000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>43499</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>43499</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>43499</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>36750</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>36750</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>36749</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>36749</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>43499</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>43499</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -5998,1236 +7227,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>36750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -7271,7 +7271,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -7310,7 +7310,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -7349,7 +7349,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -7388,7 +7388,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -7432,7 +7432,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -7471,7 +7471,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -7510,7 +7510,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -7549,7 +7549,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -7593,7 +7593,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -7832,7 +7832,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>40000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -8066,7 +8066,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>40000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -8105,7 +8105,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>40000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -8807,7 +8807,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -8963,7 +8963,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -9158,7 +9158,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -9587,7 +9587,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
       <xdr:row>60</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -9665,7 +9665,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
       <xdr:row>62</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -9704,7 +9704,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
       <xdr:row>63</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -9743,7 +9743,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
       <xdr:row>64</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -10133,7 +10133,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
       <xdr:row>76</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -10172,7 +10172,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
       <xdr:row>77</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -10211,7 +10211,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
       <xdr:row>78</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -10250,7 +10250,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
       <xdr:row>79</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -10367,7 +10367,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
       <xdr:row>83</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -10523,7 +10523,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
       <xdr:row>87</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -10796,7 +10796,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
       <xdr:row>96</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -10835,7 +10835,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
       <xdr:row>98</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -10913,7 +10913,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
       <xdr:row>101</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -10952,7 +10952,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
       <xdr:row>102</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -10991,7 +10991,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
       <xdr:row>103</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -11108,7 +11108,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
       <xdr:row>107</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -11147,7 +11147,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>15600</xdr:colOff>
       <xdr:row>109</xdr:row>
-      <xdr:rowOff>39999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1676400" cy="942975"/>
     <xdr:pic>
@@ -11230,7 +11230,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>36749</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -11308,7 +11308,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>36750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -11347,7 +11347,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>36750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -11464,7 +11464,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -11542,7 +11542,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -11581,7 +11581,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>36750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -11620,7 +11620,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -11659,7 +11659,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -11698,7 +11698,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -11737,7 +11737,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -11776,7 +11776,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -11815,7 +11815,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -11854,7 +11854,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -11893,7 +11893,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>36750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -11932,7 +11932,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>36750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -11971,7 +11971,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>36750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -12010,7 +12010,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>36750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -12049,7 +12049,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>36750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -12127,7 +12127,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -12166,7 +12166,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -12205,7 +12205,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -12244,7 +12244,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>36749</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -12283,7 +12283,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>36749</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -12322,7 +12322,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>36749</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -12361,7 +12361,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>36749</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -12400,7 +12400,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>36749</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -12444,7 +12444,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -12483,7 +12483,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -12522,7 +12522,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -12561,7 +12561,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -12600,7 +12600,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -12639,7 +12639,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -12678,7 +12678,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -12717,7 +12717,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -12756,7 +12756,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -12795,7 +12795,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -12834,7 +12834,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -12873,7 +12873,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -12912,7 +12912,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -12951,7 +12951,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -12990,7 +12990,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -13029,7 +13029,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -13068,7 +13068,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -13107,7 +13107,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>36750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -13146,7 +13146,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>36750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -13185,7 +13185,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -13224,7 +13224,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -13263,7 +13263,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -13302,7 +13302,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -13341,7 +13341,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -13380,7 +13380,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -13419,7 +13419,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>36749</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -13458,7 +13458,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -13497,7 +13497,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -13536,7 +13536,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>36749</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -13575,7 +13575,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>36749</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -13614,7 +13614,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>36749</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -13653,7 +13653,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>36749</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -13692,7 +13692,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>36749</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -13736,7 +13736,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>36749</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -13775,7 +13775,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>36749</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -13814,7 +13814,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>36749</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -13853,7 +13853,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>36750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -13892,7 +13892,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>36750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -13931,7 +13931,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>36750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -13970,7 +13970,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>36750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -14009,7 +14009,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>36750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -14048,7 +14048,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>36750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -14087,7 +14087,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>36750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -14126,7 +14126,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>36750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -14165,7 +14165,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>36750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -14204,7 +14204,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>36750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -14243,7 +14243,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>36750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -14282,7 +14282,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>36750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -14321,7 +14321,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>36750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -14360,7 +14360,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>36750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -14399,7 +14399,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>36750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -14438,7 +14438,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -14477,7 +14477,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>36750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -14516,7 +14516,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -14555,7 +14555,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -14594,7 +14594,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -14711,7 +14711,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>36749</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -14833,7 +14833,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -14872,7 +14872,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -14911,7 +14911,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
+      <xdr:rowOff>43499</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -14950,7 +14950,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -14989,7 +14989,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>36750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -15028,7 +15028,1304 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>10</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Picture 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Picture 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Picture 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="Picture 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="Picture 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="Picture 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>36749</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>36749</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>32000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>36750</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>36750</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>36750</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>32000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>36750</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>36750</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>36750</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>36750</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>36750</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>36750</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>36750</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Picture 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>43499</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>36749</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>43499</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>36750</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="762000" cy="762000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7800</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -15106,7 +16403,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -15184,7 +16481,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -15223,1304 +16520,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Picture 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Picture 14">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="Picture 15">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="Picture 16">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="Picture 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="Picture 18">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="19" name="Picture 19">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Picture 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Picture 14">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>31999</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="762000" cy="762000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>7800</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -16559,7 +16559,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -16598,7 +16598,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -16637,7 +16637,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -16676,7 +16676,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -16715,7 +16715,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -16876,7 +16876,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>36750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -16993,7 +16993,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>43500</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -17071,7 +17071,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>7800</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>32000</xdr:rowOff>
+      <xdr:rowOff>36750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="762000" cy="762000"/>
     <xdr:pic>
@@ -17447,7 +17447,7 @@
     <col min="9" max="9" width="38" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="20" customWidth="1"/>
+    <col min="12" max="12" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -18737,7 +18737,7 @@
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="9" width="13" customWidth="1"/>
     <col min="10" max="10" width="26" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -18827,7 +18827,7 @@
       <c r="K5" s="26"/>
       <c r="L5" s="26"/>
     </row>
-    <row r="6" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
         <v>1103</v>
@@ -18863,7 +18863,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="7" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="15" t="s">
         <v>1107</v>
@@ -18899,7 +18899,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="8" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
       <c r="B8" s="7" t="s">
         <v>1111</v>
@@ -18951,7 +18951,7 @@
       <c r="K9" s="26"/>
       <c r="L9" s="26"/>
     </row>
-    <row r="10" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="7" t="s">
         <v>1114</v>
@@ -19003,7 +19003,7 @@
       <c r="K11" s="26"/>
       <c r="L11" s="26"/>
     </row>
-    <row r="12" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
       <c r="B12" s="7" t="s">
         <v>1116</v>
@@ -19039,7 +19039,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="13" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="14"/>
       <c r="B13" s="15" t="s">
         <v>1117</v>
@@ -19091,7 +19091,7 @@
       <c r="K14" s="26"/>
       <c r="L14" s="26"/>
     </row>
-    <row r="15" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
       <c r="B15" s="7" t="s">
         <v>1120</v>
@@ -19143,7 +19143,7 @@
       <c r="K16" s="26"/>
       <c r="L16" s="26"/>
     </row>
-    <row r="17" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
       <c r="B17" s="7" t="s">
         <v>1124</v>
@@ -19219,7 +19219,7 @@
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="9" width="13" customWidth="1"/>
     <col min="10" max="10" width="26" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -19309,7 +19309,7 @@
       <c r="K5" s="26"/>
       <c r="L5" s="26"/>
     </row>
-    <row r="6" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
         <v>1130</v>
@@ -19345,7 +19345,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="7" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="15" t="s">
         <v>1132</v>
@@ -19381,7 +19381,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="8" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
       <c r="B8" s="7" t="s">
         <v>1134</v>
@@ -19433,7 +19433,7 @@
       <c r="K9" s="26"/>
       <c r="L9" s="26"/>
     </row>
-    <row r="10" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="7" t="s">
         <v>1137</v>
@@ -19469,7 +19469,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="11" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="14"/>
       <c r="B11" s="15" t="s">
         <v>1141</v>
@@ -19505,7 +19505,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="12" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
       <c r="B12" s="7" t="s">
         <v>1143</v>
@@ -19541,7 +19541,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="13" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="14"/>
       <c r="B13" s="15" t="s">
         <v>1145</v>
@@ -19629,7 +19629,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="16" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="14"/>
       <c r="B16" s="15" t="s">
         <v>1151</v>
@@ -19665,7 +19665,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="17" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
       <c r="B17" s="7" t="s">
         <v>1154</v>
@@ -19717,7 +19717,7 @@
       <c r="K18" s="26"/>
       <c r="L18" s="26"/>
     </row>
-    <row r="19" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="6"/>
       <c r="B19" s="7" t="s">
         <v>1156</v>
@@ -19753,7 +19753,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="20" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="14"/>
       <c r="B20" s="15" t="s">
         <v>1158</v>
@@ -19834,7 +19834,7 @@
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="9" width="13" customWidth="1"/>
     <col min="10" max="10" width="26" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -19924,7 +19924,7 @@
       <c r="K5" s="26"/>
       <c r="L5" s="26"/>
     </row>
-    <row r="6" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
         <v>1162</v>
@@ -19960,7 +19960,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="7" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="15" t="s">
         <v>1165</v>
@@ -19996,7 +19996,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="8" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
       <c r="B8" s="7" t="s">
         <v>1168</v>
@@ -20032,7 +20032,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="9" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="14"/>
       <c r="B9" s="15" t="s">
         <v>1170</v>
@@ -20084,7 +20084,7 @@
       <c r="K10" s="26"/>
       <c r="L10" s="26"/>
     </row>
-    <row r="11" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" s="7" t="s">
         <v>1173</v>
@@ -20136,7 +20136,7 @@
       <c r="K12" s="26"/>
       <c r="L12" s="26"/>
     </row>
-    <row r="13" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
       <c r="B13" s="7" t="s">
         <v>1177</v>
@@ -20170,7 +20170,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="14" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="14"/>
       <c r="B14" s="15" t="s">
         <v>1181</v>
@@ -20243,7 +20243,7 @@
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="9" width="13" customWidth="1"/>
     <col min="10" max="10" width="26" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -20333,7 +20333,7 @@
       <c r="K5" s="26"/>
       <c r="L5" s="26"/>
     </row>
-    <row r="6" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
         <v>1183</v>
@@ -20385,7 +20385,7 @@
       <c r="K7" s="26"/>
       <c r="L7" s="26"/>
     </row>
-    <row r="8" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
       <c r="B8" s="7" t="s">
         <v>1187</v>
@@ -20437,7 +20437,7 @@
       <c r="K9" s="26"/>
       <c r="L9" s="26"/>
     </row>
-    <row r="10" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="7" t="s">
         <v>1189</v>
@@ -20473,7 +20473,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="11" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="14"/>
       <c r="B11" s="15" t="s">
         <v>1192</v>
@@ -20543,7 +20543,7 @@
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="9" width="13" customWidth="1"/>
     <col min="10" max="10" width="26" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -20633,7 +20633,7 @@
       <c r="K5" s="26"/>
       <c r="L5" s="26"/>
     </row>
-    <row r="6" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
         <v>1196</v>
@@ -20669,7 +20669,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="7" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="15" t="s">
         <v>1199</v>
@@ -20705,7 +20705,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="8" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
       <c r="B8" s="7" t="s">
         <v>1201</v>
@@ -20807,7 +20807,7 @@
       <c r="K11" s="26"/>
       <c r="L11" s="26"/>
     </row>
-    <row r="12" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
       <c r="B12" s="7" t="s">
         <v>1207</v>
@@ -20878,7 +20878,7 @@
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="9" width="13" customWidth="1"/>
     <col min="10" max="10" width="26" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -20968,7 +20968,7 @@
       <c r="K5" s="26"/>
       <c r="L5" s="26"/>
     </row>
-    <row r="6" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
         <v>1212</v>
@@ -21020,7 +21020,7 @@
       <c r="K7" s="26"/>
       <c r="L7" s="26"/>
     </row>
-    <row r="8" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
       <c r="B8" s="7" t="s">
         <v>1214</v>
@@ -21056,7 +21056,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="9" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="14"/>
       <c r="B9" s="15" t="s">
         <v>1218</v>
@@ -21106,7 +21106,7 @@
       <c r="K10" s="26"/>
       <c r="L10" s="26"/>
     </row>
-    <row r="11" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" s="7" t="s">
         <v>1221</v>
@@ -21176,7 +21176,7 @@
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="9" width="13" customWidth="1"/>
     <col min="10" max="10" width="26" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -21266,7 +21266,7 @@
       <c r="K5" s="26"/>
       <c r="L5" s="26"/>
     </row>
-    <row r="6" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
         <v>1226</v>
@@ -21302,7 +21302,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="7" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="15" t="s">
         <v>1229</v>
@@ -21338,7 +21338,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="8" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
       <c r="B8" s="7" t="s">
         <v>1229</v>
@@ -21374,7 +21374,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="9" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="14"/>
       <c r="B9" s="15" t="s">
         <v>1231</v>
@@ -21444,7 +21444,7 @@
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="9" width="13" customWidth="1"/>
     <col min="10" max="10" width="26" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -21534,7 +21534,7 @@
       <c r="K5" s="26"/>
       <c r="L5" s="26"/>
     </row>
-    <row r="6" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
         <v>1234</v>
@@ -21601,7 +21601,7 @@
     <col min="8" max="8" width="38" customWidth="1"/>
     <col min="9" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="20" customWidth="1"/>
+    <col min="12" max="12" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -21870,7 +21870,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="11" ht="80" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="14"/>
       <c r="B11" s="13" t="s">
         <v>239</v>
@@ -22086,7 +22086,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="17" ht="80" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="14"/>
       <c r="B17" s="13" t="s">
         <v>275</v>
@@ -22122,7 +22122,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="18" ht="80" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
       <c r="B18" s="5" t="s">
         <v>281</v>
@@ -22802,7 +22802,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="38" ht="80" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="14"/>
       <c r="B38" s="13" t="s">
         <v>333</v>
@@ -22946,7 +22946,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="42" ht="80" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="14"/>
       <c r="B42" s="13" t="s">
         <v>355</v>
@@ -23142,7 +23142,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="48" ht="80" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="6"/>
       <c r="B48" s="5" t="s">
         <v>381</v>
@@ -23570,7 +23570,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="61" ht="80" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="14"/>
       <c r="B61" s="13" t="s">
         <v>442</v>
@@ -23642,7 +23642,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="63" ht="80" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="14"/>
       <c r="B63" s="13" t="s">
         <v>454</v>
@@ -23678,7 +23678,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="64" ht="80" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="6"/>
       <c r="B64" s="5" t="s">
         <v>459</v>
@@ -23714,7 +23714,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="65" ht="80" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="14"/>
       <c r="B65" s="13" t="s">
         <v>465</v>
@@ -24106,7 +24106,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="77" ht="80" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="6"/>
       <c r="B77" s="5" t="s">
         <v>513</v>
@@ -24142,7 +24142,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="78" ht="80" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="14"/>
       <c r="B78" s="13" t="s">
         <v>518</v>
@@ -24178,7 +24178,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="79" ht="80" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="6"/>
       <c r="B79" s="5" t="s">
         <v>524</v>
@@ -24214,7 +24214,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="80" ht="80" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="14"/>
       <c r="B80" s="13" t="s">
         <v>530</v>
@@ -24338,7 +24338,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="84" ht="80" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="14"/>
       <c r="B84" s="13" t="s">
         <v>549</v>
@@ -24482,7 +24482,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="88" ht="80" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" s="14"/>
       <c r="B88" s="13" t="s">
         <v>567</v>
@@ -24766,7 +24766,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="97" ht="80" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" s="6"/>
       <c r="B97" s="5" t="s">
         <v>600</v>
@@ -24818,7 +24818,7 @@
       <c r="K98" s="4"/>
       <c r="L98" s="4"/>
     </row>
-    <row r="99" ht="80" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="6"/>
       <c r="B99" s="5" t="s">
         <v>607</v>
@@ -24906,7 +24906,7 @@
       <c r="K101" s="4"/>
       <c r="L101" s="4"/>
     </row>
-    <row r="102" ht="80" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" s="6"/>
       <c r="B102" s="5" t="s">
         <v>620</v>
@@ -24942,7 +24942,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="103" ht="80" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" s="14"/>
       <c r="B103" s="13" t="s">
         <v>625</v>
@@ -24978,7 +24978,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="104" ht="80" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" s="6"/>
       <c r="B104" s="5" t="s">
         <v>631</v>
@@ -25102,7 +25102,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="108" ht="80" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" s="6"/>
       <c r="B108" s="5" t="s">
         <v>49</v>
@@ -25154,7 +25154,7 @@
       <c r="K109" s="4"/>
       <c r="L109" s="4"/>
     </row>
-    <row r="110" ht="80" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" s="6"/>
       <c r="B110" s="5" t="s">
         <v>33</v>
@@ -25232,7 +25232,7 @@
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="9" width="13" customWidth="1"/>
     <col min="10" max="10" width="26" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -25358,7 +25358,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="7" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="15" t="s">
         <v>665</v>
@@ -25430,7 +25430,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="9" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="14"/>
       <c r="B9" s="15" t="s">
         <v>673</v>
@@ -25466,7 +25466,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="10" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="7" t="s">
         <v>677</v>
@@ -25574,7 +25574,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="13" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="14"/>
       <c r="B13" s="15" t="s">
         <v>685</v>
@@ -25646,7 +25646,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="15" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="14"/>
       <c r="B15" s="15" t="s">
         <v>693</v>
@@ -25682,7 +25682,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="16" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" s="7" t="s">
         <v>695</v>
@@ -25732,7 +25732,7 @@
       <c r="K17" s="26"/>
       <c r="L17" s="26"/>
     </row>
-    <row r="18" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
       <c r="B18" s="7" t="s">
         <v>700</v>
@@ -25768,7 +25768,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="19" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="14"/>
       <c r="B19" s="15" t="s">
         <v>703</v>
@@ -25804,7 +25804,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="20" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="7" t="s">
         <v>706</v>
@@ -25840,7 +25840,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="21" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="14"/>
       <c r="B21" s="15" t="s">
         <v>709</v>
@@ -25876,7 +25876,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="22" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="6"/>
       <c r="B22" s="7" t="s">
         <v>712</v>
@@ -25912,7 +25912,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="23" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="14"/>
       <c r="B23" s="15" t="s">
         <v>715</v>
@@ -25948,7 +25948,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="24" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="6"/>
       <c r="B24" s="7" t="s">
         <v>719</v>
@@ -25998,7 +25998,7 @@
       <c r="K25" s="26"/>
       <c r="L25" s="26"/>
     </row>
-    <row r="26" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="6"/>
       <c r="B26" s="7" t="s">
         <v>723</v>
@@ -26034,7 +26034,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="27" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="14"/>
       <c r="B27" s="15" t="s">
         <v>727</v>
@@ -26086,7 +26086,7 @@
       <c r="K28" s="26"/>
       <c r="L28" s="26"/>
     </row>
-    <row r="29" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="7" t="s">
         <v>733</v>
@@ -26122,7 +26122,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="30" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="14"/>
       <c r="B30" s="15" t="s">
         <v>736</v>
@@ -26158,7 +26158,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="31" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
       <c r="B31" s="7" t="s">
         <v>740</v>
@@ -26260,7 +26260,7 @@
       <c r="K34" s="26"/>
       <c r="L34" s="26"/>
     </row>
-    <row r="35" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="6"/>
       <c r="B35" s="7" t="s">
         <v>748</v>
@@ -26296,7 +26296,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="36" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="14"/>
       <c r="B36" s="15" t="s">
         <v>751</v>
@@ -26330,7 +26330,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="37" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="6"/>
       <c r="B37" s="7" t="s">
         <v>754</v>
@@ -26380,7 +26380,7 @@
       <c r="K38" s="26"/>
       <c r="L38" s="26"/>
     </row>
-    <row r="39" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="6"/>
       <c r="B39" s="7" t="s">
         <v>757</v>
@@ -26432,7 +26432,7 @@
       <c r="K40" s="26"/>
       <c r="L40" s="26"/>
     </row>
-    <row r="41" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="6"/>
       <c r="B41" s="7" t="s">
         <v>761</v>
@@ -26468,7 +26468,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="42" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="14"/>
       <c r="B42" s="15" t="s">
         <v>764</v>
@@ -26504,7 +26504,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="43" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="6"/>
       <c r="B43" s="7" t="s">
         <v>766</v>
@@ -26540,7 +26540,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="44" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="14"/>
       <c r="B44" s="15" t="s">
         <v>768</v>
@@ -26645,7 +26645,7 @@
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="9" width="13" customWidth="1"/>
     <col min="10" max="10" width="26" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -26735,7 +26735,7 @@
       <c r="K5" s="26"/>
       <c r="L5" s="26"/>
     </row>
-    <row r="6" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
         <v>772</v>
@@ -26771,7 +26771,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="7" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="15" t="s">
         <v>775</v>
@@ -26807,7 +26807,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="8" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
       <c r="B8" s="7" t="s">
         <v>778</v>
@@ -26843,7 +26843,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="9" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="14"/>
       <c r="B9" s="15" t="s">
         <v>781</v>
@@ -26879,7 +26879,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="10" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="7" t="s">
         <v>784</v>
@@ -26915,7 +26915,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="11" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="14"/>
       <c r="B11" s="15" t="s">
         <v>786</v>
@@ -26951,7 +26951,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="12" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
       <c r="B12" s="7" t="s">
         <v>788</v>
@@ -26987,7 +26987,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="13" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="14"/>
       <c r="B13" s="15" t="s">
         <v>791</v>
@@ -27023,7 +27023,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="14" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
       <c r="B14" s="7" t="s">
         <v>794</v>
@@ -27059,7 +27059,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="15" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="14"/>
       <c r="B15" s="15" t="s">
         <v>797</v>
@@ -27095,7 +27095,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="16" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" s="7" t="s">
         <v>800</v>
@@ -27131,7 +27131,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="17" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="14"/>
       <c r="B17" s="15" t="s">
         <v>802</v>
@@ -27167,7 +27167,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="18" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
       <c r="B18" s="7" t="s">
         <v>805</v>
@@ -27217,7 +27217,7 @@
       <c r="K19" s="26"/>
       <c r="L19" s="26"/>
     </row>
-    <row r="20" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="7" t="s">
         <v>809</v>
@@ -27253,7 +27253,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="21" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="14"/>
       <c r="B21" s="15" t="s">
         <v>813</v>
@@ -27289,7 +27289,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="22" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="6"/>
       <c r="B22" s="7" t="s">
         <v>816</v>
@@ -27325,7 +27325,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="23" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="14"/>
       <c r="B23" s="15" t="s">
         <v>818</v>
@@ -27377,7 +27377,7 @@
       <c r="K24" s="26"/>
       <c r="L24" s="26"/>
     </row>
-    <row r="25" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="6"/>
       <c r="B25" s="7" t="s">
         <v>820</v>
@@ -27413,7 +27413,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="26" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="14"/>
       <c r="B26" s="15" t="s">
         <v>824</v>
@@ -27449,7 +27449,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="27" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="7" t="s">
         <v>827</v>
@@ -27485,7 +27485,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="28" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="14"/>
       <c r="B28" s="15" t="s">
         <v>830</v>
@@ -27521,7 +27521,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="29" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="7" t="s">
         <v>832</v>
@@ -27557,7 +27557,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="30" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="14"/>
       <c r="B30" s="15" t="s">
         <v>834</v>
@@ -27593,7 +27593,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="31" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
       <c r="B31" s="7" t="s">
         <v>835</v>
@@ -27629,7 +27629,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="32" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="14"/>
       <c r="B32" s="15" t="s">
         <v>837</v>
@@ -27681,7 +27681,7 @@
       <c r="K33" s="26"/>
       <c r="L33" s="26"/>
     </row>
-    <row r="34" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="6"/>
       <c r="B34" s="7" t="s">
         <v>840</v>
@@ -27733,7 +27733,7 @@
       <c r="K35" s="26"/>
       <c r="L35" s="26"/>
     </row>
-    <row r="36" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="6"/>
       <c r="B36" s="7" t="s">
         <v>844</v>
@@ -27785,7 +27785,7 @@
       <c r="K37" s="26"/>
       <c r="L37" s="26"/>
     </row>
-    <row r="38" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="6"/>
       <c r="B38" s="7" t="s">
         <v>847</v>
@@ -27837,7 +27837,7 @@
       <c r="K39" s="26"/>
       <c r="L39" s="26"/>
     </row>
-    <row r="40" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="6"/>
       <c r="B40" s="7" t="s">
         <v>850</v>
@@ -27873,7 +27873,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="41" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="14"/>
       <c r="B41" s="15" t="s">
         <v>853</v>
@@ -27909,7 +27909,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="42" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="6"/>
       <c r="B42" s="7" t="s">
         <v>855</v>
@@ -27945,7 +27945,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="43" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="14"/>
       <c r="B43" s="15" t="s">
         <v>857</v>
@@ -27981,7 +27981,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="44" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="6"/>
       <c r="B44" s="7" t="s">
         <v>859</v>
@@ -28084,7 +28084,7 @@
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="9" width="13" customWidth="1"/>
     <col min="10" max="10" width="26" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -28174,7 +28174,7 @@
       <c r="K5" s="26"/>
       <c r="L5" s="26"/>
     </row>
-    <row r="6" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
         <v>863</v>
@@ -28210,7 +28210,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="7" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="15" t="s">
         <v>867</v>
@@ -28246,7 +28246,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="8" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
       <c r="B8" s="7" t="s">
         <v>871</v>
@@ -28282,7 +28282,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="9" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="14"/>
       <c r="B9" s="15" t="s">
         <v>874</v>
@@ -28318,7 +28318,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="10" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="7" t="s">
         <v>878</v>
@@ -28354,7 +28354,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="11" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="14"/>
       <c r="B11" s="15" t="s">
         <v>881</v>
@@ -28390,7 +28390,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="12" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
       <c r="B12" s="7" t="s">
         <v>884</v>
@@ -28426,7 +28426,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="13" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="14"/>
       <c r="B13" s="15" t="s">
         <v>887</v>
@@ -28462,7 +28462,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="14" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
       <c r="B14" s="7" t="s">
         <v>890</v>
@@ -28498,7 +28498,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="15" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="14"/>
       <c r="B15" s="15" t="s">
         <v>892</v>
@@ -28534,7 +28534,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="16" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" s="7" t="s">
         <v>893</v>
@@ -28568,7 +28568,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="17" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="14"/>
       <c r="B17" s="15" t="s">
         <v>895</v>
@@ -28604,7 +28604,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="18" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
       <c r="B18" s="7" t="s">
         <v>896</v>
@@ -28640,7 +28640,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="19" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="14"/>
       <c r="B19" s="15" t="s">
         <v>898</v>
@@ -28676,7 +28676,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="20" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="7" t="s">
         <v>900</v>
@@ -28728,7 +28728,7 @@
       <c r="K21" s="26"/>
       <c r="L21" s="26"/>
     </row>
-    <row r="22" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="6"/>
       <c r="B22" s="7" t="s">
         <v>903</v>
@@ -28764,7 +28764,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="23" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="14"/>
       <c r="B23" s="15" t="s">
         <v>905</v>
@@ -28800,7 +28800,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="24" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="6"/>
       <c r="B24" s="7" t="s">
         <v>908</v>
@@ -28836,7 +28836,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="25" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="14"/>
       <c r="B25" s="15" t="s">
         <v>910</v>
@@ -28872,7 +28872,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="26" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="6"/>
       <c r="B26" s="7" t="s">
         <v>913</v>
@@ -28922,7 +28922,7 @@
       <c r="K27" s="26"/>
       <c r="L27" s="26"/>
     </row>
-    <row r="28" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
       <c r="B28" s="7" t="s">
         <v>917</v>
@@ -28958,7 +28958,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="29" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="14"/>
       <c r="B29" s="15" t="s">
         <v>921</v>
@@ -28994,7 +28994,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="30" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
       <c r="B30" s="7" t="s">
         <v>923</v>
@@ -29134,7 +29134,7 @@
       <c r="K34" s="26"/>
       <c r="L34" s="26"/>
     </row>
-    <row r="35" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="6"/>
       <c r="B35" s="7" t="s">
         <v>931</v>
@@ -29321,7 +29321,7 @@
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="9" width="13" customWidth="1"/>
     <col min="10" max="10" width="26" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -29411,7 +29411,7 @@
       <c r="K5" s="26"/>
       <c r="L5" s="26"/>
     </row>
-    <row r="6" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
         <v>943</v>
@@ -29447,7 +29447,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="7" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="15" t="s">
         <v>948</v>
@@ -29483,7 +29483,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="8" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
       <c r="B8" s="7" t="s">
         <v>950</v>
@@ -29519,7 +29519,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="9" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="14"/>
       <c r="B9" s="15" t="s">
         <v>951</v>
@@ -29555,7 +29555,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="10" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="7" t="s">
         <v>952</v>
@@ -29591,7 +29591,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="11" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="14"/>
       <c r="B11" s="15" t="s">
         <v>955</v>
@@ -29627,7 +29627,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="12" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
       <c r="B12" s="7" t="s">
         <v>957</v>
@@ -29663,7 +29663,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="13" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="14"/>
       <c r="B13" s="15" t="s">
         <v>959</v>
@@ -29699,7 +29699,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="14" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
       <c r="B14" s="7" t="s">
         <v>961</v>
@@ -29751,7 +29751,7 @@
       <c r="K15" s="26"/>
       <c r="L15" s="26"/>
     </row>
-    <row r="16" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" s="7" t="s">
         <v>964</v>
@@ -29787,7 +29787,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="17" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="14"/>
       <c r="B17" s="15" t="s">
         <v>966</v>
@@ -29823,7 +29823,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="18" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
       <c r="B18" s="7" t="s">
         <v>967</v>
@@ -29859,7 +29859,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="19" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="14"/>
       <c r="B19" s="15" t="s">
         <v>969</v>
@@ -29895,7 +29895,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="20" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="7" t="s">
         <v>971</v>
@@ -29931,7 +29931,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="21" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="14"/>
       <c r="B21" s="15" t="s">
         <v>973</v>
@@ -29983,7 +29983,7 @@
       <c r="K22" s="26"/>
       <c r="L22" s="26"/>
     </row>
-    <row r="23" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="6"/>
       <c r="B23" s="7" t="s">
         <v>976</v>
@@ -30035,7 +30035,7 @@
       <c r="K24" s="26"/>
       <c r="L24" s="26"/>
     </row>
-    <row r="25" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="6"/>
       <c r="B25" s="7" t="s">
         <v>979</v>
@@ -30087,7 +30087,7 @@
       <c r="K26" s="26"/>
       <c r="L26" s="26"/>
     </row>
-    <row r="27" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="7" t="s">
         <v>984</v>
@@ -30123,7 +30123,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="28" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="14"/>
       <c r="B28" s="15" t="s">
         <v>988</v>
@@ -30212,7 +30212,7 @@
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="9" width="13" customWidth="1"/>
     <col min="10" max="10" width="26" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -30302,7 +30302,7 @@
       <c r="K5" s="26"/>
       <c r="L5" s="26"/>
     </row>
-    <row r="6" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
         <v>991</v>
@@ -30338,7 +30338,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="7" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="15" t="s">
         <v>994</v>
@@ -30426,7 +30426,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="10" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="14"/>
       <c r="B10" s="15" t="s">
         <v>999</v>
@@ -30462,7 +30462,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="11" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" s="7" t="s">
         <v>1002</v>
@@ -30498,7 +30498,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="12" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="14"/>
       <c r="B12" s="15" t="s">
         <v>1004</v>
@@ -30570,7 +30570,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="14" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="14"/>
       <c r="B14" s="15" t="s">
         <v>1007</v>
@@ -30622,7 +30622,7 @@
       <c r="K15" s="26"/>
       <c r="L15" s="26"/>
     </row>
-    <row r="16" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" s="7" t="s">
         <v>1009</v>
@@ -30658,7 +30658,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="17" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="14"/>
       <c r="B17" s="15" t="s">
         <v>1013</v>
@@ -30710,7 +30710,7 @@
       <c r="K18" s="26"/>
       <c r="L18" s="26"/>
     </row>
-    <row r="19" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="6"/>
       <c r="B19" s="7" t="s">
         <v>1017</v>
@@ -30762,7 +30762,7 @@
       <c r="K20" s="26"/>
       <c r="L20" s="26"/>
     </row>
-    <row r="21" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
       <c r="B21" s="7" t="s">
         <v>1021</v>
@@ -30798,7 +30798,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="22" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="14"/>
       <c r="B22" s="15" t="s">
         <v>1023</v>
@@ -30832,7 +30832,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="23" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="6"/>
       <c r="B23" s="7" t="s">
         <v>1026</v>
@@ -30916,7 +30916,7 @@
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="9" width="13" customWidth="1"/>
     <col min="10" max="10" width="26" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -31006,7 +31006,7 @@
       <c r="K5" s="26"/>
       <c r="L5" s="26"/>
     </row>
-    <row r="6" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
         <v>1031</v>
@@ -31042,7 +31042,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="7" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="15" t="s">
         <v>1034</v>
@@ -31078,7 +31078,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="8" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
       <c r="B8" s="7" t="s">
         <v>1037</v>
@@ -31114,7 +31114,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="9" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="14"/>
       <c r="B9" s="15" t="s">
         <v>1039</v>
@@ -31150,7 +31150,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="10" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="7" t="s">
         <v>1041</v>
@@ -31186,7 +31186,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="11" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="14"/>
       <c r="B11" s="15" t="s">
         <v>1043</v>
@@ -31256,7 +31256,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="13" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="14"/>
       <c r="B13" s="15" t="s">
         <v>1048</v>
@@ -31344,7 +31344,7 @@
       <c r="K15" s="26"/>
       <c r="L15" s="26"/>
     </row>
-    <row r="16" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" s="7" t="s">
         <v>1052</v>
@@ -31380,7 +31380,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="17" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="14"/>
       <c r="B17" s="15" t="s">
         <v>1054</v>
@@ -31432,7 +31432,7 @@
       <c r="K18" s="26"/>
       <c r="L18" s="26"/>
     </row>
-    <row r="19" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="6"/>
       <c r="B19" s="7" t="s">
         <v>1056</v>
@@ -31468,7 +31468,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="20" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="14"/>
       <c r="B20" s="15" t="s">
         <v>1060</v>
@@ -31520,7 +31520,7 @@
       <c r="K21" s="26"/>
       <c r="L21" s="26"/>
     </row>
-    <row r="22" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="6"/>
       <c r="B22" s="7" t="s">
         <v>1065</v>
@@ -31556,7 +31556,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="23" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="14"/>
       <c r="B23" s="15" t="s">
         <v>1068</v>
@@ -31608,7 +31608,7 @@
       <c r="K24" s="26"/>
       <c r="L24" s="26"/>
     </row>
-    <row r="25" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="6"/>
       <c r="B25" s="7" t="s">
         <v>1071</v>
@@ -31694,7 +31694,7 @@
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="9" width="13" customWidth="1"/>
     <col min="10" max="10" width="26" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -31924,7 +31924,7 @@
       <c r="K10" s="26"/>
       <c r="L10" s="26"/>
     </row>
-    <row r="11" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" s="7" t="s">
         <v>1084</v>
@@ -32048,7 +32048,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="15" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" ht="87" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
       <c r="B15" s="7" t="s">
         <v>1092</v>
@@ -32134,7 +32134,7 @@
       <c r="K17" s="26"/>
       <c r="L17" s="26"/>
     </row>
-    <row r="18" ht="64" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" ht="73.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
       <c r="B18" s="7" t="s">
         <v>1098</v>
